--- a/Inputs/PyDump.xlsx
+++ b/Inputs/PyDump.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Documents\WORK\GCOH\GCOH-Tickets-for-Processing\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4F48F7-754D-4400-BCB6-ABCCDEB9BB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3CC3B2-7DAB-41FB-91A3-B1D8B4667FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
   <si>
     <t>Object</t>
   </si>
@@ -43,55 +43,31 @@
     <t>Ticket</t>
   </si>
   <si>
-    <t>PLEAN_X370221DE6515200 OGS COM Other</t>
+    <t>CNOW_7210$$$0000010277</t>
   </si>
   <si>
-    <t>PLEAN_X370231DE6511200 EZM COM Advertising</t>
+    <t>G000001621</t>
   </si>
   <si>
-    <t>CSCALA_1042$MSMS_O22</t>
+    <t>CNOW_7210$$$0000010278</t>
   </si>
   <si>
-    <t>CSCALA_1042$ONPM_O69</t>
+    <t>G000001620</t>
   </si>
   <si>
-    <t>CSCALA_1042$ONPM_W14</t>
+    <t>CNOW_7210$$$0000010279</t>
   </si>
   <si>
-    <t>CSCALA_1042$MSMS_F17</t>
+    <t>CNOW_7210$$$0000010280</t>
   </si>
   <si>
-    <t>CSCALA_1042$MSPM_E87</t>
+    <t>G000001618</t>
   </si>
   <si>
-    <t>CSCALA_1042$MSPM_E88</t>
+    <t>CNOW_7210$$$0000010281</t>
   </si>
   <si>
-    <t>CSCALA_1042$MSPM_E89</t>
-  </si>
-  <si>
-    <t>CSCALA_1042$MSMS_D53</t>
-  </si>
-  <si>
-    <t>CSCALA_1042$MSIS_S58</t>
-  </si>
-  <si>
-    <t>CSCALA_1820$A030_H99</t>
-  </si>
-  <si>
-    <t>H000004415</t>
-  </si>
-  <si>
-    <t>H000004416</t>
-  </si>
-  <si>
-    <t>H000001244</t>
-  </si>
-  <si>
-    <t>H000005168</t>
-  </si>
-  <si>
-    <t>FR8818680</t>
+    <t>FR8843860</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1111,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9544D389-BCBF-4017-8282-1DF88DB28091}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" bestFit="1" customWidth="1"/>
@@ -1159,164 +1135,54 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
         <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Inputs/PyDump.xlsx
+++ b/Inputs/PyDump.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Documents\WORK\GCOH\GCOH-Tickets-for-Processing\Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M289204\Documents\GCOH\GCOH-Tickets-for-Processing\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3CC3B2-7DAB-41FB-91A3-B1D8B4667FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82DB1E1-7EFD-4EB0-983E-2BAE27D561F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
   </bookViews>
   <sheets>
     <sheet name="Dump" sheetId="1" r:id="rId1"/>
@@ -19,20 +19,28 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dump!$A$1:$C$1</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"caea3f49-dfad-4101-9423-d5e90b427b0f"</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="104">
   <si>
     <t>Object</t>
   </si>
@@ -43,31 +51,307 @@
     <t>Ticket</t>
   </si>
   <si>
-    <t>CNOW_7210$$$0000010277</t>
-  </si>
-  <si>
-    <t>G000001621</t>
-  </si>
-  <si>
-    <t>CNOW_7210$$$0000010278</t>
-  </si>
-  <si>
-    <t>G000001620</t>
-  </si>
-  <si>
-    <t>CNOW_7210$$$0000010279</t>
-  </si>
-  <si>
-    <t>CNOW_7210$$$0000010280</t>
-  </si>
-  <si>
-    <t>G000001618</t>
-  </si>
-  <si>
-    <t>CNOW_7210$$$0000010281</t>
-  </si>
-  <si>
-    <t>FR8843860</t>
+    <t>CORAERP_MMOR1975.9424 9424 Strategy, Bus Dev, Transformation Mgmt</t>
+  </si>
+  <si>
+    <t>L000011353 Strategic Program Management</t>
+  </si>
+  <si>
+    <t>CPHOENX_01010000683000 LS Strategy</t>
+  </si>
+  <si>
+    <t>L000011344 Strategy &amp; Market Intelligence</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000056419 Strategy &amp; Transformation Head Office</t>
+  </si>
+  <si>
+    <t>CPHOENX_01010000697781 LS Transformation Office</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000020761 Integration Bio-Techne</t>
+  </si>
+  <si>
+    <t>L000014145 Bio-Techne Integration</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.9506 9506 Integration Bio-Techne</t>
+  </si>
+  <si>
+    <t>CPHOENX_01010000697005 Integration Bio-Techne</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000010413 MERCK INTEGRATION PLANNING OFFICE</t>
+  </si>
+  <si>
+    <t>L000013683 Deleted Other LS Mngt</t>
+  </si>
+  <si>
+    <t>CSCALA_1025$CON2 DELETED</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000052353 GIN - Marine cargo / Trans</t>
+  </si>
+  <si>
+    <t>L000011242 Other -G</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000058227 MY GROUP INSURANCE</t>
+  </si>
+  <si>
+    <t>CEMERAL_64010010991303 President office General</t>
+  </si>
+  <si>
+    <t>L000011191 Local Functions -G</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006112OTZ010 Other accounting common</t>
+  </si>
+  <si>
+    <t>CEMERAL_700063029905PC Marketing department</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1059C000 Site Manager Office</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1059C01000 Operation-CCM Production-Non-Production Depreciation and Oth</t>
+  </si>
+  <si>
+    <t>L000011158 IPR Amortization -G</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1059C01002 Operation-CCM Production-PC02 Depreciation</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1059C01004 Operation-CCM Production-PC04 Depreciation</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1059C01006 Operation-CCM Production-PC06 Depreciation</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1059C01007 Operation-CCM Production-PC07 Depreciation</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1059C030 Operation-Supply Chain Management Department</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1059C040 Operation-QA&amp;QC</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1059C050 Operation-EHS</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1059C060 Operation-Engineering</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1798A20 rent HCMC</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1798A21 rent Han</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000000135 Cost Center Variances - Bonus</t>
+  </si>
+  <si>
+    <t>L000013890 Placeholder 3</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000001008 Bonus Accrual Release CCV</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000006008 Bonus Accrual Release  R&amp;D</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000008028 Bonus Accrual Release CCV</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000008068 Bonus Accrual Rel Analytics Cntr o Excel</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000009018 Bonus Accrual Release Marketing</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000010158 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000010248 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000010321 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000010440 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000020025 Tariff refund</t>
+  </si>
+  <si>
+    <t>L000013889 Tariff Refunds</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000020546 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000020681 Tariff refund</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000020716 Non Operating-TP Compensation-LS( BF-LX)</t>
+  </si>
+  <si>
+    <t>L000011157 Intercompany -G</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000021310 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000021311 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000022250 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000023443 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000023444 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000025529 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000025530 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000026990 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000040119 AIP accrual adjustment &amp; release</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000040988 Non Operating-TP Compensation-LS( BF-C4)</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000052108 TP Compensation - H7</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000052181 Bank Charges CH International</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000056142 Bank Charges</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000057900 TP compensation C4</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000058206 MY RS COS Expenses</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000261221 C4 - Cost Center Variances</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000261223 C4 - Internal Sales Services</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000261224 C4 - R&amp;D expenses Global</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000261225 C4 - Group Information Service</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000261230 Gene Tox shut down costs</t>
+  </si>
+  <si>
+    <t>L000011155 Integration Projects (OTC) -G</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000499010 Bonus Accrual Release CCV</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000499011 Bonus Accrual Release Global Tech</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000499012 Bonus Accrual Release Internal Sales</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000499014 Bonus Accrual Release HR</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000499015 Bonus Accrual Release IT</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000499016 Bonus Accrual Release R&amp;D</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0024061221 C4 - Cost Center Variances</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0024061222 C4 - Order Processing and Logistics</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0024061223 C4 - Internal Sales Services</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0024061225 C4 - Group Information Service</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0024061226 C4 - Finance</t>
+  </si>
+  <si>
+    <t>CNOW_ROW$$$$0000009999 JP SAP balance</t>
+  </si>
+  <si>
+    <t>CNOW_ROW$$$$0079581000 JP MD office</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1922.CGUS CGUS Corporate Management</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.SUSP SUSP Suspense Account</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.2940 2940 LS tariff refund</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.J5VT J5VT BL J5 Downstream -  Merck Korea</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.P1QA P1QA BL P1 Aseptic - Merck KGaA</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.P1UK P1UK BL P1 Aseptic - UK</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.Q9KO Q9KO BL Q9 Services - KO</t>
+  </si>
+  <si>
+    <t>CPHOENX_01010000697908 LS Bridge</t>
+  </si>
+  <si>
+    <t>CSCALA_1759$CAMI</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000CH70ADKI01 LF Other Admin Costs AL</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000DE90140080 XXXRestructuring and transition costs</t>
+  </si>
+  <si>
+    <t>CTEMPLA_1000CO10100098 LF-Employee Experien</t>
+  </si>
+  <si>
+    <t>CTEMPNA_1000US10000030 Fin - Cash Discount Retained</t>
+  </si>
+  <si>
+    <t>CEMERAL_70007001433248 MESI REG BP FERTILITY-MEDICAL NON-RD</t>
+  </si>
+  <si>
+    <t>H000000688 Global R&amp;D Direct Costs</t>
+  </si>
+  <si>
+    <t>FR8846529</t>
+  </si>
+  <si>
+    <t>FR8841303</t>
   </si>
 </sst>
 </file>
@@ -814,9 +1098,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -854,7 +1138,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -960,7 +1244,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1102,7 +1386,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1111,15 +1395,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9544D389-BCBF-4017-8282-1DF88DB28091}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C88"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1130,7 +1414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1138,10 +1422,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1149,40 +1433,942 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
+      <c r="C7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" t="s">
+        <v>37</v>
+      </c>
+      <c r="C48" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C55" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>67</v>
+      </c>
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>68</v>
+      </c>
+      <c r="B57" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" t="s">
+        <v>52</v>
+      </c>
+      <c r="C58" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>70</v>
+      </c>
+      <c r="B59" t="s">
+        <v>52</v>
+      </c>
+      <c r="C59" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>71</v>
+      </c>
+      <c r="B60" t="s">
+        <v>52</v>
+      </c>
+      <c r="C60" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>72</v>
+      </c>
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>74</v>
+      </c>
+      <c r="B62" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>76</v>
+      </c>
+      <c r="B64" t="s">
+        <v>37</v>
+      </c>
+      <c r="C64" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>77</v>
+      </c>
+      <c r="B65" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>78</v>
+      </c>
+      <c r="B66" t="s">
+        <v>37</v>
+      </c>
+      <c r="C66" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>79</v>
+      </c>
+      <c r="B67" t="s">
+        <v>37</v>
+      </c>
+      <c r="C67" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>80</v>
+      </c>
+      <c r="B68" t="s">
+        <v>52</v>
+      </c>
+      <c r="C68" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>81</v>
+      </c>
+      <c r="B69" t="s">
+        <v>52</v>
+      </c>
+      <c r="C69" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>82</v>
+      </c>
+      <c r="B70" t="s">
+        <v>52</v>
+      </c>
+      <c r="C70" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>83</v>
+      </c>
+      <c r="B71" t="s">
+        <v>52</v>
+      </c>
+      <c r="C71" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>84</v>
+      </c>
+      <c r="B72" t="s">
+        <v>52</v>
+      </c>
+      <c r="C72" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>85</v>
+      </c>
+      <c r="B73" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>86</v>
+      </c>
+      <c r="B74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>87</v>
+      </c>
+      <c r="B75" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>88</v>
+      </c>
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>89</v>
+      </c>
+      <c r="B77" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>90</v>
+      </c>
+      <c r="B78" t="s">
+        <v>52</v>
+      </c>
+      <c r="C78" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>91</v>
+      </c>
+      <c r="B79" t="s">
+        <v>52</v>
+      </c>
+      <c r="C79" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>92</v>
+      </c>
+      <c r="B80" t="s">
+        <v>52</v>
+      </c>
+      <c r="C80" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>93</v>
+      </c>
+      <c r="B81" t="s">
+        <v>52</v>
+      </c>
+      <c r="C81" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" t="s">
+        <v>73</v>
+      </c>
+      <c r="C82" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>95</v>
+      </c>
+      <c r="B83" t="s">
+        <v>52</v>
+      </c>
+      <c r="C83" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>96</v>
+      </c>
+      <c r="B84" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>97</v>
+      </c>
+      <c r="B85" t="s">
+        <v>73</v>
+      </c>
+      <c r="C85" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>98</v>
+      </c>
+      <c r="B86" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>99</v>
+      </c>
+      <c r="B87" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>100</v>
+      </c>
+      <c r="B88" t="s">
+        <v>101</v>
+      </c>
+      <c r="C88" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Inputs/PyDump.xlsx
+++ b/Inputs/PyDump.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M289204\Documents\GCOH\GCOH-Tickets-for-Processing\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4230AB0E-BEFF-4052-BDA2-17334CB5D90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4799A63-8580-4EDA-8B8C-43B4AC43B780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" firstSheet="1" activeTab="1" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dump" sheetId="1" r:id="rId1"/>
+    <sheet name="Cognos_Office_Connection_Cache" sheetId="2" state="veryHidden" r:id="rId1"/>
+    <sheet name="Dump" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dump!$A$1:$C$1</definedName>
-    <definedName name="ID" localSheetId="0" hidden="1">"caea3f49-dfad-4101-9423-d5e90b427b0f"</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Dump!$A$1:$C$1</definedName>
+    <definedName name="ID" localSheetId="0" hidden="1">"cc91e4ec-5087-46ad-be42-e95d99828779"</definedName>
+    <definedName name="ID" localSheetId="1" hidden="1">"caea3f49-dfad-4101-9423-d5e90b427b0f"</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Object</t>
   </si>
@@ -51,19 +53,13 @@
     <t>Ticket</t>
   </si>
   <si>
-    <t>PLEAN_L00420529ES</t>
+    <t>CEMERAL_70007001586003 MESI REG PS-TECH &amp; SCI SOL APAC</t>
   </si>
   <si>
-    <t>H000004470</t>
+    <t>L000011673</t>
   </si>
   <si>
-    <t>PLEAN_L00420530ES</t>
-  </si>
-  <si>
-    <t>H000004471</t>
-  </si>
-  <si>
-    <t>FR8846961</t>
+    <t>FR8852160</t>
   </si>
 </sst>
 </file>
@@ -1105,9 +1101,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BF5FEE-4834-415E-A288-F1664A2A6DF0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9544D389-BCBF-4017-8282-1DF88DB28091}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="51.81640625" bestFit="1" customWidth="1"/>
@@ -1134,18 +1139,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Inputs/PyDump.xlsx
+++ b/Inputs/PyDump.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M289204\Documents\GCOH\GCOH-Tickets-for-Processing\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4799A63-8580-4EDA-8B8C-43B4AC43B780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968594D6-832A-4D8A-8D81-BA4DEF4B5C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" firstSheet="1" activeTab="1" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
   </bookViews>
   <sheets>
     <sheet name="Cognos_Office_Connection_Cache" sheetId="2" state="veryHidden" r:id="rId1"/>
@@ -53,13 +53,13 @@
     <t>Ticket</t>
   </si>
   <si>
-    <t>CEMERAL_70007001586003 MESI REG PS-TECH &amp; SCI SOL APAC</t>
+    <t>PLEAN_L00420003ES</t>
   </si>
   <si>
-    <t>L000011673</t>
+    <t>H000000902</t>
   </si>
   <si>
-    <t>FR8852160</t>
+    <t>FR8859555</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1103,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BF5FEE-4834-415E-A288-F1664A2A6DF0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1113,14 +1113,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9544D389-BCBF-4017-8282-1DF88DB28091}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/Inputs/PyDump.xlsx
+++ b/Inputs/PyDump.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M289204\Documents\GCOH\GCOH-Tickets-for-Processing\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968594D6-832A-4D8A-8D81-BA4DEF4B5C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9FDEE9-66F6-428D-B557-E4090EAFE21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
   <si>
     <t>Object</t>
   </si>
@@ -53,13 +53,85 @@
     <t>Ticket</t>
   </si>
   <si>
-    <t>PLEAN_L00420003ES</t>
-  </si>
-  <si>
-    <t>H000000902</t>
-  </si>
-  <si>
-    <t>FR8859555</t>
+    <t>CFLTFLE_23732373XXXX</t>
+  </si>
+  <si>
+    <t>L000012278</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424CC1 test</t>
+  </si>
+  <si>
+    <t>L000013912</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR010 Sales Revenue</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR031 Import Product Cost</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR0323 Samples</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR0332 Price Difference On</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR0334 Cons. &amp; Util. Var.</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR051 Sales - person. exp.</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR053 BD IVD - pers. exp.</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR055 Sales - other costs</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR057 BD IVD - other costs</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR060 R&amp;D - person. exp.</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR061 R&amp;D - other costs</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR070 Floating royalty</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR071 Transfer price adjustments</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR080 Depr. Int. Fixed Assets</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR082 Deprec Accounts rece</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR083 Manual corr. Deprec.</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR500 Special integration costs (production related)</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR501 Special integration costs (marketing &amp; selling related)</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR502 Special integration costs (administration related)</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR503 Special integration costs (research &amp; development related)</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2424JSR504 Special integration costs (investering related)</t>
+  </si>
+  <si>
+    <t>FR8877587</t>
+  </si>
+  <si>
+    <t>FR8879675</t>
   </si>
 </sst>
 </file>
@@ -1112,7 +1184,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9544D389-BCBF-4017-8282-1DF88DB28091}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" bestFit="1" customWidth="1"/>
@@ -1139,7 +1211,249 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Inputs/PyDump.xlsx
+++ b/Inputs/PyDump.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M289204\Documents\GCOH\GCOH-Tickets-for-Processing\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9FDEE9-66F6-428D-B557-E4090EAFE21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768BE333-8D9F-4105-96AE-85A70C6ABFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t>Object</t>
   </si>
@@ -53,85 +53,40 @@
     <t>Ticket</t>
   </si>
   <si>
-    <t>CFLTFLE_23732373XXXX</t>
-  </si>
-  <si>
-    <t>L000012278</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424CC1 test</t>
-  </si>
-  <si>
-    <t>L000013912</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR010 Sales Revenue</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR031 Import Product Cost</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR0323 Samples</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR0332 Price Difference On</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR0334 Cons. &amp; Util. Var.</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR051 Sales - person. exp.</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR053 BD IVD - pers. exp.</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR055 Sales - other costs</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR057 BD IVD - other costs</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR060 R&amp;D - person. exp.</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR061 R&amp;D - other costs</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR070 Floating royalty</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR071 Transfer price adjustments</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR080 Depr. Int. Fixed Assets</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR082 Deprec Accounts rece</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR083 Manual corr. Deprec.</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR500 Special integration costs (production related)</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR501 Special integration costs (marketing &amp; selling related)</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR502 Special integration costs (administration related)</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR503 Special integration costs (research &amp; development related)</t>
-  </si>
-  <si>
-    <t>CFLTFLE_2424JSR504 Special integration costs (investering related)</t>
-  </si>
-  <si>
-    <t>FR8877587</t>
-  </si>
-  <si>
-    <t>FR8879675</t>
+    <t>CSCALA_1042$CSCC</t>
+  </si>
+  <si>
+    <t>G000001602</t>
+  </si>
+  <si>
+    <t>CSCALA_1042$CSCC_999</t>
+  </si>
+  <si>
+    <t>CSCALA_1042$CSCC_P19</t>
+  </si>
+  <si>
+    <t>CSCALA_1042$CSCC_P49</t>
+  </si>
+  <si>
+    <t>CSCALA_1042$DXRM</t>
+  </si>
+  <si>
+    <t>L000013994</t>
+  </si>
+  <si>
+    <t>CSCALA_1042$EDP_P55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G000000635 </t>
+  </si>
+  <si>
+    <t>CSCALA_1042$LSPE</t>
+  </si>
+  <si>
+    <t>L000013905</t>
+  </si>
+  <si>
+    <t>FR8878279</t>
   </si>
 </sst>
 </file>
@@ -339,7 +294,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -543,8 +498,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -689,6 +650,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -769,8 +741,10 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="69">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1184,7 +1158,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9544D389-BCBF-4017-8282-1DF88DB28091}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" bestFit="1" customWidth="1"/>
@@ -1204,256 +1178,80 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
-        <v>6</v>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1461,7 +1259,7 @@
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A1048576">
+  <conditionalFormatting sqref="A9:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="243"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Inputs/PyDump.xlsx
+++ b/Inputs/PyDump.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M289204\Documents\GCOH\GCOH-Tickets-for-Processing\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768BE333-8D9F-4105-96AE-85A70C6ABFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3887B06-3E1A-4D28-A745-2272B70C1EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="349">
   <si>
     <t>Object</t>
   </si>
@@ -53,40 +53,1042 @@
     <t>Ticket</t>
   </si>
   <si>
-    <t>CSCALA_1042$CSCC</t>
-  </si>
-  <si>
-    <t>G000001602</t>
-  </si>
-  <si>
-    <t>CSCALA_1042$CSCC_999</t>
-  </si>
-  <si>
-    <t>CSCALA_1042$CSCC_P19</t>
-  </si>
-  <si>
-    <t>CSCALA_1042$CSCC_P49</t>
-  </si>
-  <si>
-    <t>CSCALA_1042$DXRM</t>
-  </si>
-  <si>
-    <t>L000013994</t>
-  </si>
-  <si>
-    <t>CSCALA_1042$EDP_P55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G000000635 </t>
-  </si>
-  <si>
-    <t>CSCALA_1042$LSPE</t>
-  </si>
-  <si>
-    <t>L000013905</t>
-  </si>
-  <si>
-    <t>FR8878279</t>
+    <t>CTEMPLA_1000CL10794210</t>
+  </si>
+  <si>
+    <t>G000001529</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.9000</t>
+  </si>
+  <si>
+    <t>G000000318</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000PL80GBTL17</t>
+  </si>
+  <si>
+    <t>G000000324</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000PT10A52109</t>
+  </si>
+  <si>
+    <t>G000001714</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000PL80GBTL23</t>
+  </si>
+  <si>
+    <t>G000000786</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000PL80GBTL24</t>
+  </si>
+  <si>
+    <t>CTEMPLA_1000EC10100140</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.9926</t>
+  </si>
+  <si>
+    <t>CSCALA_1826$852_CCM</t>
+  </si>
+  <si>
+    <t>G000000244</t>
+  </si>
+  <si>
+    <t>CSCALA_1025$GEIT_A01</t>
+  </si>
+  <si>
+    <t>CSCALA_1820$Q352_Q09</t>
+  </si>
+  <si>
+    <t>H000001146</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000056329</t>
+  </si>
+  <si>
+    <t>G000000152</t>
+  </si>
+  <si>
+    <t>CSCALA_1042$BMSE</t>
+  </si>
+  <si>
+    <t>L000013190</t>
+  </si>
+  <si>
+    <t>CSCALA_1042$BMMC</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6599 6599 BioC MA R&amp;D</t>
+  </si>
+  <si>
+    <t>L000014188</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6605 6605 Next Generation Processing (R&amp;D)</t>
+  </si>
+  <si>
+    <t>L000006631</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6605 6605 Next Generation Processing (R&amp;D)</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203600706 SDD Head + Operations</t>
+  </si>
+  <si>
+    <t>L000006519</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000010467 BioC PAD US SIAL</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6596 6596 US - PBB RD</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6996 6996 PS SDD Legacy &amp; Acquired Technologies Development Team</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203600701 Biocontinuum Program Management</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6059 6059 Software &amp; Automation</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6708 6708 Software Automation</t>
+  </si>
+  <si>
+    <t>L000014215</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6708 6708 Software Automation</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203600702 Legacy &amp; Acquired Technologies Dev Team</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203600704 Enterprise Architecture</t>
+  </si>
+  <si>
+    <t>L000014187</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203990106 Infrastructure &amp; Shared Services</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203600703 ART Development Team</t>
+  </si>
+  <si>
+    <t>L000014189</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6995 6995 PS SDD ART Development Team</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6996 6996 PS SDD Legacy &amp; Acquired Technologies Development Team</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6998 6998 PS SDD Enterprise Architecture</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6995 6995 PS SDD ART Development Team</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6998 6998 PS SDD Enterprise Architecture</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000052154 ART Development Team</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6733 6733 Vercors Process Automation &amp; Delivery</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6059 6059 Software &amp; Automation</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6992 6992 PS SDD</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6992 6992 PS SDD</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203400903 BioContinuum P Transformation</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6045 6045 Bioprocessing R&amp;D Management</t>
+  </si>
+  <si>
+    <t>L000006611</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000022106 STL SAFC CELL CULTURE R&amp;D MGMT</t>
+  </si>
+  <si>
+    <t>L000013510</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006101RD3107 SU/Systems R&amp;D - China</t>
+  </si>
+  <si>
+    <t>L000014195</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6121 6121 Integrated Perfusion Bioreactor</t>
+  </si>
+  <si>
+    <t>L000014191</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6587 6587 SU/Systems - MAST</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6587 6587 SU/Systems - MAST</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6593 6593 SU/Systems - Breez Engineering &amp; Systems Technology</t>
+  </si>
+  <si>
+    <t>L000014196</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000FR60640000 SUIS R&amp;D - Applications (Pessac)</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6546 6546 Single-Use Technology Management</t>
+  </si>
+  <si>
+    <t>L000014193</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6549 6549 Single-Use Systems</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6121 6121 Integrated Perfusion Bioreactor</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6502 6502 Single Use Products</t>
+  </si>
+  <si>
+    <t>L000014192</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6546 6546 Single-Use Technology Management</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6549 6549 Single-Use Systems</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6510 6510 R&amp;D Engineering Services</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6572 6572 Cell Culture Sciences &amp; Protein Eng</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1099.6993 6993 FDS - Development Engineering</t>
+  </si>
+  <si>
+    <t>L000006647</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6993 6993 FDS - Development Engineering</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006101RD3103 GENM - FDS Product Engineering</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1099.6994 6994 FDS - Product Engineering</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6994 6994 FDS - Product Engineering</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6502 6502 Single Use Products</t>
+  </si>
+  <si>
+    <t>CSCALA_1923$B44 GENM - FDS R&amp;D Product Engineering</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6732 6732 Vercors Single Use &amp; Integrated Systems</t>
+  </si>
+  <si>
+    <t>L000014194</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6306 6306 Validation &amp; Application Center (VAC)</t>
+  </si>
+  <si>
+    <t>L000014199</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6613 6613 Bioanalytical Technologies (BAT)</t>
+  </si>
+  <si>
+    <t>L000014198</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6745 6745 StrategicInitiative R&amp;D Ops</t>
+  </si>
+  <si>
+    <t>L000014202</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6306 6306 Validation &amp; Application Center (VAC)</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6043 6043 Analytical Technologies</t>
+  </si>
+  <si>
+    <t>L000014197</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6204 6204 Virology &amp; Microbiology Sciences</t>
+  </si>
+  <si>
+    <t>L000014200</t>
+  </si>
+  <si>
+    <t>D30006300000000 R&amp;D support for ISCO</t>
+  </si>
+  <si>
+    <t>L000014203</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6027 6027 Filtration R&amp;D - Applications</t>
+  </si>
+  <si>
+    <t>L000014204</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6505 6505 Filtration R&amp;D - Virus Safety</t>
+  </si>
+  <si>
+    <t>L000006622</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6509 6509 Filtration R&amp;D - Aseptic</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6511 6511 Filtration R&amp;D - Ultrafiltration</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6542 6542 Filtration R&amp;D - Clarification</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6568 6568 Filtration R&amp;D - Industrialization</t>
+  </si>
+  <si>
+    <t>D30006200000000 Viresolve Pro 2.0</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6103 6103 Natrix (R&amp;D)</t>
+  </si>
+  <si>
+    <t>L000006641</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6536 6536 R&amp;D Purification</t>
+  </si>
+  <si>
+    <t>D30009900000000 Natrix A</t>
+  </si>
+  <si>
+    <t>L000006642</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000021322 Analytical R&amp;D</t>
+  </si>
+  <si>
+    <t>L000014205</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000022302 BioP - Cell Line Inventory</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006101RD3101 Upstream Technology Center (China)</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000021104 STL SAFC R&amp;D CELL CULTURE</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000022105 STL SAFC CSD</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000022107 SAFC CHOZN R&amp;D</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000025755 LNX MEDIA DEVELOPMENT</t>
+  </si>
+  <si>
+    <t>L000014207</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000025758 Cell Culture Media R&amp;D (Lenexa)</t>
+  </si>
+  <si>
+    <t>L000014206</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000020562 Viral Vectors &amp; Producer Cell Lines Prod</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006101MS3106 A&amp;F Applic. Lab China</t>
+  </si>
+  <si>
+    <t>L000014209</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203600811 Application Lab A&amp;F</t>
+  </si>
+  <si>
+    <t>L000014210</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000041 CH71 Folate R&amp;D &amp; Studies</t>
+  </si>
+  <si>
+    <t>L000013131</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000049 CH71 Activities for Marketing</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000062 CH71 13C-Labeled Folates</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000076 CH71 C_Modufolin-Cancer- Isofol</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000098 CH71 T_PET Tracer</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000107 CH71 General Activities</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000108 CH71 Desktop Research</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000109 CH71 P_ Arcofolin R&amp;D Support</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000162 CH71 REV 13C-Labeled Folates</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000163 CH71 REV Reference Substances</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000438 CH71 P_Arcofolin - Pre-eclampsia</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000461 XXXCH71 T_Arcofolin Depression</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000501 CH71 P_ Arcofolin API</t>
+  </si>
+  <si>
+    <t>TEMPEU_1000CH70RD1100 Synthesis &amp; Development API (SH)</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6201 6201 GENM - CELL THERAPY BIOP. R&amp;D</t>
+  </si>
+  <si>
+    <t>L000014211</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6594 6594 SU/Systems - Breez Applications</t>
+  </si>
+  <si>
+    <t>L000014213</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6611 6611 USP Templates, Scale Up, Team Supply</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6612 6612 DSP Templates, Scale Up, &amp; PD</t>
+  </si>
+  <si>
+    <t>L000014212</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.5968 5968 US MSAT Application Engineering</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.5240 5240 PS GSA EMEA</t>
+  </si>
+  <si>
+    <t>L000012329</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000DE40MS3001 GSA Scientific specialist</t>
+  </si>
+  <si>
+    <t>L000012332</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6637 6637 PS innovation office</t>
+  </si>
+  <si>
+    <t>L000012359</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000020545 GENM - Project Management Office</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000025458 PMO (CFP)</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.6047 6047 PMO PDP</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.6047 6047 PMO PDP</t>
+  </si>
+  <si>
+    <t>L000014241</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.5444 5444 Single Use Core</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.5444 5444 Single Use Core</t>
+  </si>
+  <si>
+    <t>L000014245</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.5299 5299 Marketing - Hardware &amp; Systems</t>
+  </si>
+  <si>
+    <t>L000014243</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.5070 5070 BioC Marketing</t>
+  </si>
+  <si>
+    <t>L000014244</t>
+  </si>
+  <si>
+    <t>CEMERAL_70007001584949 REG Downstream Chrom</t>
+  </si>
+  <si>
+    <t>L000013555</t>
+  </si>
+  <si>
+    <t>CEMERAL_70007001586003 MESI REG PS-TECH &amp; SCI SOL APAC</t>
+  </si>
+  <si>
+    <t>L000013910</t>
+  </si>
+  <si>
+    <t>CEMERAL_64010010860642 Process Solutions/Provantage Lab</t>
+  </si>
+  <si>
+    <t>L000014249</t>
+  </si>
+  <si>
+    <t>CEMERAL_64010010860644 PS Provantage Lab E&amp;L</t>
+  </si>
+  <si>
+    <t>CEMERAL_64010010860643 PS Provantage Lab Quality</t>
+  </si>
+  <si>
+    <t>L000014251</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203600101 COGS -Service - BPS - Provantage Lab</t>
+  </si>
+  <si>
+    <t>L000014248</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203600108 Provantage India E&amp;L</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203600107 Provantage India Quality</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203600109 Provantage India GTS</t>
+  </si>
+  <si>
+    <t>L000014252</t>
+  </si>
+  <si>
+    <t>CTEMPLA_1000MX10332002 BVS Mexico VPM</t>
+  </si>
+  <si>
+    <t>L000014250</t>
+  </si>
+  <si>
+    <t>CTEMPLA_1000BR10704400 BVS Brazil VPM</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.3029 3029 NAM ProV Lab - Retention</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.3471 3471 NAM ProV Lab - E&amp;L</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.3080 3080 EU ProV Lab</t>
+  </si>
+  <si>
+    <t>L000014247</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.3453 3453 EU ProV Lab - VPC</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.5793 5793 VS France</t>
+  </si>
+  <si>
+    <t>L000013860</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.3455 3455 EU ProV Lab - Quality</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.5117 5117 BVS France GTS</t>
+  </si>
+  <si>
+    <t>CEMERAL_700061019901B2 Provantage Lab</t>
+  </si>
+  <si>
+    <t>L000014246</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006101FS1101 Provantage Quality China</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.3543 3543 PS GSO Quality</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.3544 3544 PS GS Validation Services</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006101FS1102 Provantage China E&amp;L</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1044RACS Order Processing - R&amp;A  Cutomer Service</t>
+  </si>
+  <si>
+    <t>L000011882</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1798C01 Customer service</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.5640 5640 Research Sales Support &amp; Specialty Business</t>
+  </si>
+  <si>
+    <t>L000014219</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000020380 STL RE US eCOMMERCE IMPLEMENTATION</t>
+  </si>
+  <si>
+    <t>L000014237</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000021313 Research SS &amp; Specialty</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000NL40CS1016 NL - Custome Care</t>
+  </si>
+  <si>
+    <t>L000014221</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000NL40CS1007 CS North</t>
+  </si>
+  <si>
+    <t>CSCALA_1042$CSD LS Customer Service</t>
+  </si>
+  <si>
+    <t>CSCALA_1042$LSCC Life Science Credit Control</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000058233 Research &amp; Applied - Customer Service</t>
+  </si>
+  <si>
+    <t>CSCALA_1759$PEOC</t>
+  </si>
+  <si>
+    <t>L000014222</t>
+  </si>
+  <si>
+    <t>CSCALA_1759$CHTA</t>
+  </si>
+  <si>
+    <t>CSCALA_1759$GICA</t>
+  </si>
+  <si>
+    <t>CEMERAL_64010010861112 CE Customer Service</t>
+  </si>
+  <si>
+    <t>L000008405</t>
+  </si>
+  <si>
+    <t>CNOW_ROW$$$$0000002302 CE Customer Service</t>
+  </si>
+  <si>
+    <t>CNOW_ROW$$$$0000006200 CE Process Excellence</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000NL40CS1001 CS WEST</t>
+  </si>
+  <si>
+    <t>CEMERAL_64010010971101 CE Process Excellence</t>
+  </si>
+  <si>
+    <t>CFLTFLE_10548-172-CCC CUSTOMER CARE CENTER</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000NL40MS1170 RE WE CEX Sales support</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000NL40CS1006 CS WE Business Process</t>
+  </si>
+  <si>
+    <t>L000014238</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000NL40MS2007 PS Process Excellence</t>
+  </si>
+  <si>
+    <t>L000013530</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000NL40CS1002 CS Credit Mgt</t>
+  </si>
+  <si>
+    <t>L000014228</t>
+  </si>
+  <si>
+    <t>L000008791</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1975.9531 9531 SFDC PMO</t>
+  </si>
+  <si>
+    <t>L000014232</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000025534 Operational Excellence Lenexa</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000007125 NA Sales Suppport (Customer Service)</t>
+  </si>
+  <si>
+    <t>L000014217</t>
+  </si>
+  <si>
+    <t>CEMERAL_70007001184361 MESI LS-ORD &amp; SCM</t>
+  </si>
+  <si>
+    <t>CEMERAL_70007001184363 MESI LS - ORD &amp; SCM - C&amp;C</t>
+  </si>
+  <si>
+    <t>CEMERAL_70007001184362 MESI LS-FF SALES SUPPORT</t>
+  </si>
+  <si>
+    <t>CEMERAL_70007102171425 PS Customer Excellence</t>
+  </si>
+  <si>
+    <t>L000014226</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000015030 Cash Collection CE WE</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000015210 DE Customer Service - 1</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000015232 DE Dealer Export CSS</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000015209 RA-WE-CE</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000020415 SIAL Commercial Services Ops Americas</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000FR10M39130 CEX WE Cust Focus</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000FR10MM4430 PCS sales support</t>
+  </si>
+  <si>
+    <t>L000014223</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000051592 Customer Process Excellence FR</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.5259 5259 PSC Global Sales Support and Customer Service</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000051597 Cash Collection CE WE</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.9157 9157 Customer Support Benelux &amp; Nordics</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.9552 9552 SFDC France</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.5844 5844 CEx Regional Sales Support</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.9779 9779 SLS Cex  Customer Process Excellence</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.9128 9128 EU CS - Export/Eastern</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000051566 FR Customer Service Front Line</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.5978 5978 CEx WE Customer Support South</t>
+  </si>
+  <si>
+    <t>CEMERAL_70007001584301 MESI REG PS-ORDER PROCESSING &amp; SCM</t>
+  </si>
+  <si>
+    <t>L000008439</t>
+  </si>
+  <si>
+    <t>CEMERAL_70007001184365 MESI PS-ORD &amp; SCM</t>
+  </si>
+  <si>
+    <t>CEMERAL_70007001581213 MESI REG PS-ISS PRICING</t>
+  </si>
+  <si>
+    <t>CEMERAL_700061019903CS PS Customer Excellence</t>
+  </si>
+  <si>
+    <t>L000014236</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006104414141 Business Excellence ErP Hong Kong</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000015213 DE Customer Service  - 2</t>
+  </si>
+  <si>
+    <t>CEMERAL_64010010860943 Process Solutions/Sales Support</t>
+  </si>
+  <si>
+    <t>CTEMPLA_1000AR10220012 Customer Excellence PS</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203801110 CE PS</t>
+  </si>
+  <si>
+    <t>L000008383</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006502961441 PS Customer Excellence South Korea</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006502991732 Customer Excellence</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1044LSCL Order Processing - Collection team Lifescience and PM</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1044PSCE Order Processing - Process Solutions  Customer Service</t>
+  </si>
+  <si>
+    <t>CTEMPLA_1000MX10317045 PS Customer Excellence</t>
+  </si>
+  <si>
+    <t>L000011809</t>
+  </si>
+  <si>
+    <t>CTEMPLA_1000PE10400001 Customer Excellence Peru</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000TR10FS1240 PS-Customer Excellence</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000TR10SD1201 CS TR</t>
+  </si>
+  <si>
+    <t>CTEMPLA_1000BR10710610 PS Customer Excellence</t>
+  </si>
+  <si>
+    <t>L000007989</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2760BGLS-L9 Customer Support &amp; Supply Chain Manager</t>
+  </si>
+  <si>
+    <t>CFLTFLE_2760BGLS-L8 Customer Support &amp; Supply Chain Officer</t>
+  </si>
+  <si>
+    <t>CNOW_AUS0$$$0000091756 Customer Excellence Shared Services</t>
+  </si>
+  <si>
+    <t>L000008299</t>
+  </si>
+  <si>
+    <t>CNOW_ROW$$$$0000091834 Customer Serv &amp; ord Fulfilment</t>
+  </si>
+  <si>
+    <t>CNOW_AUS0$$$0000091734 Customer Serv &amp; ord Fulfilment</t>
+  </si>
+  <si>
+    <t>CNOW_AUS0$$$0000091755 Customer Excellence - Process Solutions</t>
+  </si>
+  <si>
+    <t>CSCALA_1759$BRMI</t>
+  </si>
+  <si>
+    <t>CSCALA_1248$A021 CC- GR LS Logistics</t>
+  </si>
+  <si>
+    <t>CSCALA_1248$LSCS LS Customer Service EMEA RPP: 3110430000</t>
+  </si>
+  <si>
+    <t>CFLTFLE_1798C30 PSCE_VN</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006302J41401 SEA Regional Customer Excellence</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000CH70RD1100 Synthesis &amp; Development API (SH)</t>
+  </si>
+  <si>
+    <t>FTEMPEU_1000CH70RD1100_IO Synthesis &amp; Development API (SH) (IO)</t>
+  </si>
+  <si>
+    <t>TEMPEU_1000CH70RD1100_IO Synthesis &amp; Development API (SH) (IO)</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000535 Theragnostics Gen 4</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000541 R&amp;D Support of Folate Manufacturing</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003300000546 Wildcard Folate</t>
+  </si>
+  <si>
+    <t>ITEMPEU_003900000215 CH71  ITM SH 10-22002273</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000051658</t>
+  </si>
+  <si>
+    <t>L000013263</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000015340</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000040229</t>
+  </si>
+  <si>
+    <t>L000013606</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000040230</t>
+  </si>
+  <si>
+    <t>L000007793</t>
+  </si>
+  <si>
+    <t>CNOW_AUS0$$$0000092073</t>
+  </si>
+  <si>
+    <t>L000013851</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000031882</t>
+  </si>
+  <si>
+    <t>L000007973</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000010348</t>
+  </si>
+  <si>
+    <t>L000013775</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000051606</t>
+  </si>
+  <si>
+    <t>L000014145</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0024010012</t>
+  </si>
+  <si>
+    <t>L000007122</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0024010023</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0024010024</t>
+  </si>
+  <si>
+    <t>CNOW_ROW$$$$0000091845</t>
+  </si>
+  <si>
+    <t>L000005621</t>
+  </si>
+  <si>
+    <t>CNOW_ROW$$$$0000091847</t>
+  </si>
+  <si>
+    <t>L000006103</t>
+  </si>
+  <si>
+    <t>CNOW_ROW$$$$0000091846</t>
+  </si>
+  <si>
+    <t>L000006120</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000015257</t>
+  </si>
+  <si>
+    <t>L000010037</t>
+  </si>
+  <si>
+    <t>CEMERAL_7000700158120A</t>
+  </si>
+  <si>
+    <t>L000011664</t>
+  </si>
+  <si>
+    <t>FR8889047</t>
+  </si>
+  <si>
+    <t>FR8904424</t>
+  </si>
+  <si>
+    <t>FR8903279</t>
+  </si>
+  <si>
+    <t>FR8886755</t>
+  </si>
+  <si>
+    <t>FR8899612</t>
+  </si>
+  <si>
+    <t>FR8898691</t>
+  </si>
+  <si>
+    <t>FR8898693</t>
+  </si>
+  <si>
+    <t>FR8900494</t>
+  </si>
+  <si>
+    <t>FR8900331</t>
   </si>
 </sst>
 </file>
@@ -294,7 +1296,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -498,14 +1500,8 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -650,17 +1646,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -741,10 +1726,8 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="69">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1158,7 +2141,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9544D389-BCBF-4017-8282-1DF88DB28091}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" bestFit="1" customWidth="1"/>
@@ -1178,80 +2161,2687 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="C8" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="C9" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
+      <c r="C11" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>71</v>
+      </c>
+      <c r="B50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>73</v>
+      </c>
+      <c r="B51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>74</v>
+      </c>
+      <c r="B52" t="s">
+        <v>65</v>
+      </c>
+      <c r="C52" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>75</v>
+      </c>
+      <c r="B53" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>77</v>
+      </c>
+      <c r="B54" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>78</v>
+      </c>
+      <c r="B55" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>79</v>
+      </c>
+      <c r="B56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>80</v>
+      </c>
+      <c r="B57" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C58" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>83</v>
+      </c>
+      <c r="B59" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>84</v>
+      </c>
+      <c r="B60" t="s">
+        <v>82</v>
+      </c>
+      <c r="C60" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>85</v>
+      </c>
+      <c r="B61" t="s">
+        <v>82</v>
+      </c>
+      <c r="C61" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>86</v>
+      </c>
+      <c r="B62" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>87</v>
+      </c>
+      <c r="B63" t="s">
+        <v>76</v>
+      </c>
+      <c r="C63" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>88</v>
+      </c>
+      <c r="B64" t="s">
+        <v>82</v>
+      </c>
+      <c r="C64" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>89</v>
+      </c>
+      <c r="B65" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>91</v>
+      </c>
+      <c r="B66" t="s">
+        <v>92</v>
+      </c>
+      <c r="C66" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>93</v>
+      </c>
+      <c r="B67" t="s">
+        <v>94</v>
+      </c>
+      <c r="C67" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>95</v>
+      </c>
+      <c r="B68" t="s">
+        <v>96</v>
+      </c>
+      <c r="C68" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>97</v>
+      </c>
+      <c r="B69" t="s">
+        <v>92</v>
+      </c>
+      <c r="C69" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>98</v>
+      </c>
+      <c r="B70" t="s">
+        <v>99</v>
+      </c>
+      <c r="C70" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>100</v>
+      </c>
+      <c r="B71" t="s">
+        <v>101</v>
+      </c>
+      <c r="C71" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>102</v>
+      </c>
+      <c r="B72" t="s">
+        <v>103</v>
+      </c>
+      <c r="C72" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>104</v>
+      </c>
+      <c r="B73" t="s">
+        <v>105</v>
+      </c>
+      <c r="C73" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>106</v>
+      </c>
+      <c r="B74" t="s">
+        <v>107</v>
+      </c>
+      <c r="C74" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>108</v>
+      </c>
+      <c r="B75" t="s">
+        <v>107</v>
+      </c>
+      <c r="C75" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>109</v>
+      </c>
+      <c r="B76" t="s">
+        <v>107</v>
+      </c>
+      <c r="C76" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>110</v>
+      </c>
+      <c r="B77" t="s">
+        <v>107</v>
+      </c>
+      <c r="C77" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>111</v>
+      </c>
+      <c r="B78" t="s">
+        <v>103</v>
+      </c>
+      <c r="C78" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>112</v>
+      </c>
+      <c r="B79" t="s">
+        <v>107</v>
+      </c>
+      <c r="C79" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>113</v>
+      </c>
+      <c r="B80" t="s">
+        <v>114</v>
+      </c>
+      <c r="C80" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>115</v>
+      </c>
+      <c r="B81" t="s">
+        <v>114</v>
+      </c>
+      <c r="C81" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>116</v>
+      </c>
+      <c r="B82" t="s">
+        <v>117</v>
+      </c>
+      <c r="C82" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>118</v>
+      </c>
+      <c r="B83" t="s">
+        <v>119</v>
+      </c>
+      <c r="C83" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>120</v>
+      </c>
+      <c r="B84" t="s">
+        <v>119</v>
+      </c>
+      <c r="C84" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>121</v>
+      </c>
+      <c r="B85" t="s">
+        <v>119</v>
+      </c>
+      <c r="C85" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>122</v>
+      </c>
+      <c r="B86" t="s">
+        <v>119</v>
+      </c>
+      <c r="C86" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>123</v>
+      </c>
+      <c r="B87" t="s">
+        <v>119</v>
+      </c>
+      <c r="C87" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>124</v>
+      </c>
+      <c r="B88" t="s">
+        <v>119</v>
+      </c>
+      <c r="C88" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>125</v>
+      </c>
+      <c r="B89" t="s">
+        <v>126</v>
+      </c>
+      <c r="C89" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>127</v>
+      </c>
+      <c r="B90" t="s">
+        <v>128</v>
+      </c>
+      <c r="C90" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>129</v>
+      </c>
+      <c r="B91" t="s">
+        <v>119</v>
+      </c>
+      <c r="C91" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>130</v>
+      </c>
+      <c r="B92" t="s">
+        <v>131</v>
+      </c>
+      <c r="C92" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>132</v>
+      </c>
+      <c r="B93" t="s">
+        <v>133</v>
+      </c>
+      <c r="C93" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>134</v>
+      </c>
+      <c r="B94" t="s">
+        <v>135</v>
+      </c>
+      <c r="C94" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>136</v>
+      </c>
+      <c r="B95" t="s">
+        <v>135</v>
+      </c>
+      <c r="C95" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>137</v>
+      </c>
+      <c r="B96" t="s">
+        <v>135</v>
+      </c>
+      <c r="C96" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>138</v>
+      </c>
+      <c r="B97" t="s">
+        <v>135</v>
+      </c>
+      <c r="C97" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>139</v>
+      </c>
+      <c r="B98" t="s">
+        <v>135</v>
+      </c>
+      <c r="C98" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>140</v>
+      </c>
+      <c r="B99" t="s">
+        <v>135</v>
+      </c>
+      <c r="C99" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>141</v>
+      </c>
+      <c r="B100" t="s">
+        <v>135</v>
+      </c>
+      <c r="C100" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>142</v>
+      </c>
+      <c r="B101" t="s">
+        <v>135</v>
+      </c>
+      <c r="C101" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>143</v>
+      </c>
+      <c r="B102" t="s">
+        <v>135</v>
+      </c>
+      <c r="C102" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>144</v>
+      </c>
+      <c r="B103" t="s">
+        <v>135</v>
+      </c>
+      <c r="C103" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>145</v>
+      </c>
+      <c r="B104" t="s">
+        <v>135</v>
+      </c>
+      <c r="C104" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>146</v>
+      </c>
+      <c r="B105" t="s">
+        <v>135</v>
+      </c>
+      <c r="C105" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>147</v>
+      </c>
+      <c r="B106" t="s">
+        <v>135</v>
+      </c>
+      <c r="C106" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>148</v>
+      </c>
+      <c r="B107" t="s">
+        <v>135</v>
+      </c>
+      <c r="C107" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>149</v>
+      </c>
+      <c r="B108" t="s">
+        <v>150</v>
+      </c>
+      <c r="C108" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>151</v>
+      </c>
+      <c r="B109" t="s">
+        <v>152</v>
+      </c>
+      <c r="C109" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>153</v>
+      </c>
+      <c r="B110" t="s">
+        <v>150</v>
+      </c>
+      <c r="C110" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>154</v>
+      </c>
+      <c r="B111" t="s">
+        <v>155</v>
+      </c>
+      <c r="C111" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>156</v>
+      </c>
+      <c r="B112" t="s">
+        <v>155</v>
+      </c>
+      <c r="C112" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>157</v>
+      </c>
+      <c r="B113" t="s">
+        <v>158</v>
+      </c>
+      <c r="C113" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>159</v>
+      </c>
+      <c r="B114" t="s">
+        <v>160</v>
+      </c>
+      <c r="C114" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>161</v>
+      </c>
+      <c r="B115" t="s">
+        <v>39</v>
+      </c>
+      <c r="C115" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>163</v>
+      </c>
+      <c r="B116" t="s">
+        <v>162</v>
+      </c>
+      <c r="C116" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>164</v>
+      </c>
+      <c r="B117" t="s">
+        <v>162</v>
+      </c>
+      <c r="C117" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>165</v>
+      </c>
+      <c r="B118" t="s">
+        <v>162</v>
+      </c>
+      <c r="C118" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>166</v>
+      </c>
+      <c r="B119" t="s">
+        <v>162</v>
+      </c>
+      <c r="C119" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>168</v>
+      </c>
+      <c r="B120" t="s">
+        <v>167</v>
+      </c>
+      <c r="C120" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>169</v>
+      </c>
+      <c r="B121" t="s">
+        <v>170</v>
+      </c>
+      <c r="C121" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>171</v>
+      </c>
+      <c r="B122" t="s">
+        <v>172</v>
+      </c>
+      <c r="C122" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>173</v>
+      </c>
+      <c r="B123" t="s">
+        <v>174</v>
+      </c>
+      <c r="C123" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>175</v>
+      </c>
+      <c r="B124" t="s">
+        <v>176</v>
+      </c>
+      <c r="C124" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>177</v>
+      </c>
+      <c r="B125" t="s">
+        <v>178</v>
+      </c>
+      <c r="C125" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>179</v>
+      </c>
+      <c r="B126" t="s">
+        <v>180</v>
+      </c>
+      <c r="C126" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>181</v>
+      </c>
+      <c r="B127" t="s">
+        <v>180</v>
+      </c>
+      <c r="C127" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>182</v>
+      </c>
+      <c r="B128" t="s">
+        <v>183</v>
+      </c>
+      <c r="C128" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>184</v>
+      </c>
+      <c r="B129" t="s">
+        <v>185</v>
+      </c>
+      <c r="C129" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>186</v>
+      </c>
+      <c r="B130" t="s">
+        <v>185</v>
+      </c>
+      <c r="C130" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>187</v>
+      </c>
+      <c r="B131" t="s">
+        <v>183</v>
+      </c>
+      <c r="C131" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>188</v>
+      </c>
+      <c r="B132" t="s">
+        <v>189</v>
+      </c>
+      <c r="C132" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>190</v>
+      </c>
+      <c r="B133" t="s">
+        <v>191</v>
+      </c>
+      <c r="C133" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>192</v>
+      </c>
+      <c r="B134" t="s">
+        <v>191</v>
+      </c>
+      <c r="C134" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>193</v>
+      </c>
+      <c r="B135" t="s">
+        <v>191</v>
+      </c>
+      <c r="C135" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>194</v>
+      </c>
+      <c r="B136" t="s">
+        <v>191</v>
+      </c>
+      <c r="C136" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>195</v>
+      </c>
+      <c r="B137" t="s">
+        <v>196</v>
+      </c>
+      <c r="C137" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>197</v>
+      </c>
+      <c r="B138" t="s">
+        <v>196</v>
+      </c>
+      <c r="C138" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>198</v>
+      </c>
+      <c r="B139" t="s">
+        <v>199</v>
+      </c>
+      <c r="C139" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>200</v>
+      </c>
+      <c r="B140" t="s">
+        <v>183</v>
+      </c>
+      <c r="C140" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>201</v>
+      </c>
+      <c r="B141" t="s">
+        <v>189</v>
+      </c>
+      <c r="C141" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>202</v>
+      </c>
+      <c r="B142" t="s">
+        <v>203</v>
+      </c>
+      <c r="C142" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>204</v>
+      </c>
+      <c r="B143" t="s">
+        <v>183</v>
+      </c>
+      <c r="C143" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>205</v>
+      </c>
+      <c r="B144" t="s">
+        <v>183</v>
+      </c>
+      <c r="C144" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>206</v>
+      </c>
+      <c r="B145" t="s">
+        <v>189</v>
+      </c>
+      <c r="C145" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>207</v>
+      </c>
+      <c r="B146" t="s">
+        <v>203</v>
+      </c>
+      <c r="C146" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>208</v>
+      </c>
+      <c r="B147" t="s">
+        <v>209</v>
+      </c>
+      <c r="C147" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>210</v>
+      </c>
+      <c r="B148" t="s">
+        <v>209</v>
+      </c>
+      <c r="C148" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>211</v>
+      </c>
+      <c r="B149" t="s">
+        <v>212</v>
+      </c>
+      <c r="C149" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>213</v>
+      </c>
+      <c r="B150" t="s">
+        <v>214</v>
+      </c>
+      <c r="C150" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>215</v>
+      </c>
+      <c r="B151" t="s">
+        <v>212</v>
+      </c>
+      <c r="C151" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>216</v>
+      </c>
+      <c r="B152" t="s">
+        <v>217</v>
+      </c>
+      <c r="C152" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>218</v>
+      </c>
+      <c r="B153" t="s">
+        <v>217</v>
+      </c>
+      <c r="C153" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>219</v>
+      </c>
+      <c r="B154" t="s">
+        <v>209</v>
+      </c>
+      <c r="C154" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>220</v>
+      </c>
+      <c r="B155" t="s">
+        <v>209</v>
+      </c>
+      <c r="C155" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>221</v>
+      </c>
+      <c r="B156" t="s">
+        <v>209</v>
+      </c>
+      <c r="C156" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>222</v>
+      </c>
+      <c r="B157" t="s">
+        <v>223</v>
+      </c>
+      <c r="C157" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>224</v>
+      </c>
+      <c r="B158" t="s">
+        <v>223</v>
+      </c>
+      <c r="C158" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>225</v>
+      </c>
+      <c r="B159" t="s">
+        <v>223</v>
+      </c>
+      <c r="C159" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>226</v>
+      </c>
+      <c r="B160" t="s">
+        <v>227</v>
+      </c>
+      <c r="C160" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>228</v>
+      </c>
+      <c r="B161" t="s">
+        <v>227</v>
+      </c>
+      <c r="C161" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>229</v>
+      </c>
+      <c r="B162" t="s">
+        <v>227</v>
+      </c>
+      <c r="C162" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>230</v>
+      </c>
+      <c r="B163" t="s">
+        <v>217</v>
+      </c>
+      <c r="C163" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>231</v>
+      </c>
+      <c r="B164" t="s">
+        <v>227</v>
+      </c>
+      <c r="C164" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>232</v>
+      </c>
+      <c r="B165" t="s">
+        <v>209</v>
+      </c>
+      <c r="C165" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>233</v>
+      </c>
+      <c r="B166" t="s">
+        <v>217</v>
+      </c>
+      <c r="C166" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>234</v>
+      </c>
+      <c r="B167" t="s">
+        <v>235</v>
+      </c>
+      <c r="C167" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>236</v>
+      </c>
+      <c r="B168" t="s">
+        <v>237</v>
+      </c>
+      <c r="C168" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>238</v>
+      </c>
+      <c r="B169" t="s">
+        <v>239</v>
+      </c>
+      <c r="C169" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>241</v>
+      </c>
+      <c r="B170" t="s">
+        <v>242</v>
+      </c>
+      <c r="C170" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>243</v>
+      </c>
+      <c r="B171" t="s">
+        <v>214</v>
+      </c>
+      <c r="C171" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>244</v>
+      </c>
+      <c r="B172" t="s">
+        <v>245</v>
+      </c>
+      <c r="C172" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>246</v>
+      </c>
+      <c r="B173" t="s">
+        <v>209</v>
+      </c>
+      <c r="C173" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>247</v>
+      </c>
+      <c r="B174" t="s">
+        <v>209</v>
+      </c>
+      <c r="C174" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>248</v>
+      </c>
+      <c r="B175" t="s">
+        <v>209</v>
+      </c>
+      <c r="C175" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>249</v>
+      </c>
+      <c r="B176" t="s">
+        <v>250</v>
+      </c>
+      <c r="C176" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>251</v>
+      </c>
+      <c r="B177" t="s">
+        <v>217</v>
+      </c>
+      <c r="C177" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>252</v>
+      </c>
+      <c r="B178" t="s">
+        <v>217</v>
+      </c>
+      <c r="C178" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>253</v>
+      </c>
+      <c r="B179" t="s">
+        <v>240</v>
+      </c>
+      <c r="C179" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>254</v>
+      </c>
+      <c r="B180" t="s">
+        <v>242</v>
+      </c>
+      <c r="C180" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>255</v>
+      </c>
+      <c r="B181" t="s">
+        <v>245</v>
+      </c>
+      <c r="C181" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>256</v>
+      </c>
+      <c r="B182" t="s">
+        <v>217</v>
+      </c>
+      <c r="C182" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>257</v>
+      </c>
+      <c r="B183" t="s">
+        <v>258</v>
+      </c>
+      <c r="C183" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>259</v>
+      </c>
+      <c r="B184" t="s">
+        <v>235</v>
+      </c>
+      <c r="C184" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>260</v>
+      </c>
+      <c r="B185" t="s">
+        <v>258</v>
+      </c>
+      <c r="C185" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>261</v>
+      </c>
+      <c r="B186" t="s">
+        <v>217</v>
+      </c>
+      <c r="C186" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>262</v>
+      </c>
+      <c r="B187" t="s">
+        <v>217</v>
+      </c>
+      <c r="C187" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>263</v>
+      </c>
+      <c r="B188" t="s">
+        <v>214</v>
+      </c>
+      <c r="C188" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>264</v>
+      </c>
+      <c r="B189" t="s">
+        <v>217</v>
+      </c>
+      <c r="C189" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>265</v>
+      </c>
+      <c r="B190" t="s">
+        <v>235</v>
+      </c>
+      <c r="C190" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>266</v>
+      </c>
+      <c r="B191" t="s">
+        <v>240</v>
+      </c>
+      <c r="C191" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>267</v>
+      </c>
+      <c r="B192" t="s">
+        <v>217</v>
+      </c>
+      <c r="C192" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>268</v>
+      </c>
+      <c r="B193" t="s">
+        <v>217</v>
+      </c>
+      <c r="C193" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>269</v>
+      </c>
+      <c r="B194" t="s">
+        <v>270</v>
+      </c>
+      <c r="C194" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>271</v>
+      </c>
+      <c r="B195" t="s">
+        <v>270</v>
+      </c>
+      <c r="C195" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>272</v>
+      </c>
+      <c r="B196" t="s">
+        <v>214</v>
+      </c>
+      <c r="C196" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>273</v>
+      </c>
+      <c r="B197" t="s">
+        <v>274</v>
+      </c>
+      <c r="C197" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>275</v>
+      </c>
+      <c r="B198" t="s">
+        <v>214</v>
+      </c>
+      <c r="C198" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>276</v>
+      </c>
+      <c r="B199" t="s">
+        <v>217</v>
+      </c>
+      <c r="C199" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>277</v>
+      </c>
+      <c r="B200" t="s">
+        <v>227</v>
+      </c>
+      <c r="C200" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>278</v>
+      </c>
+      <c r="B201" t="s">
+        <v>245</v>
+      </c>
+      <c r="C201" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>279</v>
+      </c>
+      <c r="B202" t="s">
+        <v>280</v>
+      </c>
+      <c r="C202" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>281</v>
+      </c>
+      <c r="B203" t="s">
+        <v>270</v>
+      </c>
+      <c r="C203" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>282</v>
+      </c>
+      <c r="B204" t="s">
+        <v>270</v>
+      </c>
+      <c r="C204" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>283</v>
+      </c>
+      <c r="B205" t="s">
+        <v>209</v>
+      </c>
+      <c r="C205" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>284</v>
+      </c>
+      <c r="B206" t="s">
+        <v>209</v>
+      </c>
+      <c r="C206" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>285</v>
+      </c>
+      <c r="B207" t="s">
+        <v>286</v>
+      </c>
+      <c r="C207" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>287</v>
+      </c>
+      <c r="B208" t="s">
+        <v>286</v>
+      </c>
+      <c r="C208" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>288</v>
+      </c>
+      <c r="B209" t="s">
+        <v>258</v>
+      </c>
+      <c r="C209" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>289</v>
+      </c>
+      <c r="B210" t="s">
+        <v>240</v>
+      </c>
+      <c r="C210" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>290</v>
+      </c>
+      <c r="B211" t="s">
+        <v>291</v>
+      </c>
+      <c r="C211" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>292</v>
+      </c>
+      <c r="B212" t="s">
+        <v>223</v>
+      </c>
+      <c r="C212" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>293</v>
+      </c>
+      <c r="B213" t="s">
+        <v>223</v>
+      </c>
+      <c r="C213" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>294</v>
+      </c>
+      <c r="B214" t="s">
+        <v>295</v>
+      </c>
+      <c r="C214" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>296</v>
+      </c>
+      <c r="B215" t="s">
+        <v>295</v>
+      </c>
+      <c r="C215" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>297</v>
+      </c>
+      <c r="B216" t="s">
+        <v>295</v>
+      </c>
+      <c r="C216" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>298</v>
+      </c>
+      <c r="B217" t="s">
+        <v>250</v>
+      </c>
+      <c r="C217" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>299</v>
+      </c>
+      <c r="B218" t="s">
+        <v>223</v>
+      </c>
+      <c r="C218" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>300</v>
+      </c>
+      <c r="B219" t="s">
+        <v>223</v>
+      </c>
+      <c r="C219" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>301</v>
+      </c>
+      <c r="B220" t="s">
+        <v>223</v>
+      </c>
+      <c r="C220" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>302</v>
+      </c>
+      <c r="B221" t="s">
+        <v>209</v>
+      </c>
+      <c r="C221" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>303</v>
+      </c>
+      <c r="B222" t="s">
+        <v>209</v>
+      </c>
+      <c r="C222" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>304</v>
+      </c>
+      <c r="B223" t="s">
+        <v>135</v>
+      </c>
+      <c r="C223" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>305</v>
+      </c>
+      <c r="B224" t="s">
+        <v>135</v>
+      </c>
+      <c r="C224" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>306</v>
+      </c>
+      <c r="B225" t="s">
+        <v>135</v>
+      </c>
+      <c r="C225" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>307</v>
+      </c>
+      <c r="B226" t="s">
+        <v>135</v>
+      </c>
+      <c r="C226" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>308</v>
+      </c>
+      <c r="B227" t="s">
+        <v>135</v>
+      </c>
+      <c r="C227" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>309</v>
+      </c>
+      <c r="B228" t="s">
+        <v>135</v>
+      </c>
+      <c r="C228" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>310</v>
+      </c>
+      <c r="B229" t="s">
+        <v>135</v>
+      </c>
+      <c r="C229" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>311</v>
+      </c>
+      <c r="B230" t="s">
+        <v>312</v>
+      </c>
+      <c r="C230" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>313</v>
+      </c>
+      <c r="B231" t="s">
+        <v>312</v>
+      </c>
+      <c r="C231" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>314</v>
+      </c>
+      <c r="B232" t="s">
+        <v>315</v>
+      </c>
+      <c r="C232" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>316</v>
+      </c>
+      <c r="B233" t="s">
+        <v>317</v>
+      </c>
+      <c r="C233" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>318</v>
+      </c>
+      <c r="B234" t="s">
+        <v>319</v>
+      </c>
+      <c r="C234" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>320</v>
+      </c>
+      <c r="B235" t="s">
+        <v>321</v>
+      </c>
+      <c r="C235" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>322</v>
+      </c>
+      <c r="B236" t="s">
+        <v>323</v>
+      </c>
+      <c r="C236" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>324</v>
+      </c>
+      <c r="B237" t="s">
+        <v>325</v>
+      </c>
+      <c r="C237" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>326</v>
+      </c>
+      <c r="B238" t="s">
+        <v>327</v>
+      </c>
+      <c r="C238" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>328</v>
+      </c>
+      <c r="B239" t="s">
+        <v>327</v>
+      </c>
+      <c r="C239" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>329</v>
+      </c>
+      <c r="B240" t="s">
+        <v>327</v>
+      </c>
+      <c r="C240" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>330</v>
+      </c>
+      <c r="B241" t="s">
+        <v>331</v>
+      </c>
+      <c r="C241" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>332</v>
+      </c>
+      <c r="B242" t="s">
+        <v>333</v>
+      </c>
+      <c r="C242" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>334</v>
+      </c>
+      <c r="B243" t="s">
+        <v>335</v>
+      </c>
+      <c r="C243" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>336</v>
+      </c>
+      <c r="B244" t="s">
+        <v>337</v>
+      </c>
+      <c r="C244" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>338</v>
+      </c>
+      <c r="B245" t="s">
+        <v>339</v>
+      </c>
+      <c r="C245" t="s">
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -1259,8 +4849,8 @@
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A9:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="243"/>
+  <conditionalFormatting sqref="A2:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="244"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Inputs/PyDump.xlsx
+++ b/Inputs/PyDump.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M289204\Documents\GCOH\GCOH-Tickets-for-Processing\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E82960C-120C-4303-BB6D-74D051027517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73804670-5CA4-429A-9FE9-8358C73DC82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
+    <workbookView xWindow="6360" yWindow="2430" windowWidth="21600" windowHeight="12255" firstSheet="1" activeTab="1" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
   </bookViews>
   <sheets>
     <sheet name="Cognos_Office_Connection_Cache" sheetId="2" state="veryHidden" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Object</t>
   </si>
@@ -53,103 +53,36 @@
     <t>Ticket</t>
   </si>
   <si>
-    <t>PLEAN_X310284DE5013201 PIMI Congress EMSO</t>
+    <t>CORAERP_MMOR1945.LLQNX</t>
   </si>
   <si>
-    <t>H000005719 Rare TA Direct Costs</t>
+    <t>L000012244</t>
   </si>
   <si>
-    <t>PLEAN_X310941NO5030201 Tepmetko Commercial NO50 Other M&amp;S Regis</t>
-  </si>
-  <si>
-    <t>H000004732</t>
-  </si>
-  <si>
-    <t>PLEAN_X370221CZ5011201 Ogsiveo Commercial CZ50 Advertising Gene</t>
-  </si>
-  <si>
-    <t>H000004752</t>
-  </si>
-  <si>
-    <t>PLEAN_X370221CZ5013201 Ogsiveo Commercial CZ50 Congresses &amp; Eve</t>
-  </si>
-  <si>
-    <t>PLEAN_X370221DE5014223 OGS Global BP - GVAP</t>
-  </si>
-  <si>
-    <t>PLEAN_X370224DK5015551 RO Ogsiveo Promo &amp; advertising</t>
-  </si>
-  <si>
-    <t>H000004672</t>
-  </si>
-  <si>
-    <t>PLEAN_X370231CZ5011201 Gomekli/Ezmekly Commercial CZ50 Advertis</t>
-  </si>
-  <si>
-    <t>PLEAN_X370231DE5014201 GOM COM Strategic Initiatives</t>
-  </si>
-  <si>
-    <t>PLEAN_X370231DE5014203 GOM COM Messaging &amp; Materials</t>
-  </si>
-  <si>
-    <t>PLEAN_X370231DE5014221 GOM Global BP - IHM</t>
-  </si>
-  <si>
-    <t>PLEAN_X370231DE5014223 GOM Global BP - GVAP</t>
-  </si>
-  <si>
-    <t>CSCALA_1248$RTWE</t>
-  </si>
-  <si>
-    <t>H000005718 Rare TA Indirect Costs</t>
-  </si>
-  <si>
-    <t>CSCALA_1872$100_C45</t>
-  </si>
-  <si>
-    <t>H000003569</t>
-  </si>
-  <si>
-    <t>CSCALA_1872$140_C48</t>
-  </si>
-  <si>
-    <t>CTEMPEU_1000FR40592800 CTS REG METFORMINE</t>
-  </si>
-  <si>
-    <t>H000005839 Other IPR Holder - FB3_FR40</t>
-  </si>
-  <si>
-    <t>CTEMPEU_1000TR10AD1L31 XXXBT_Business Sector Bioharma</t>
-  </si>
-  <si>
-    <t>H000005840 Other IPR Holder - FB3_TR10</t>
-  </si>
-  <si>
-    <t>CTEMPLA_1000MX10901000 Interest expenses</t>
-  </si>
-  <si>
-    <t>H000005841 Other IPR Holder - FB3_MX10</t>
-  </si>
-  <si>
-    <t>FR8916031</t>
-  </si>
-  <si>
-    <t>FR8916015</t>
+    <t>FR8941660</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="14">
+    <numFmt numFmtId="42" formatCode="_-&quot;₱&quot;* #,##0_-;\-&quot;₱&quot;* #,##0_-;_-&quot;₱&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="###,000"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="172" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="173" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -341,8 +274,124 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF165D81"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="5" tint="0.39994506668294322"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF336577"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="6" tint="-0.24994659260841701"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="3" tint="0.39994506668294322"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Verdana Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -548,12 +597,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor rgb="FFBED7A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EFF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEFBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F4F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3D6EB"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -700,19 +785,137 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="0"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
       <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="0"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="3" tint="-0.24991607409894101"/>
+      </left>
+      <right style="thin">
+        <color theme="3" tint="-0.24991607409894101"/>
+      </right>
+      <top style="thin">
+        <color theme="3" tint="-0.24991607409894101"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="-0.24991607409894101"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color rgb="FF3BAB5A"/>
+      </left>
+      <right style="dotted">
+        <color rgb="FF3BAB5A"/>
+      </right>
+      <top style="dotted">
+        <color rgb="FF3BAB5A"/>
+      </top>
+      <bottom style="dotted">
+        <color rgb="FF3BAB5A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color rgb="FFA8A8A8"/>
+      </left>
+      <right style="dotted">
+        <color rgb="FFA8A8A8"/>
+      </right>
+      <top style="dotted">
+        <color rgb="FFA8A8A8"/>
+      </top>
+      <bottom style="dotted">
+        <color rgb="FFA8A8A8"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="69">
+  <cellStyleXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -790,12 +993,177 @@
     <xf numFmtId="0" fontId="20" fillId="36" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="37" borderId="14">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="14">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="14"/>
+    <xf numFmtId="3" fontId="31" fillId="0" borderId="14"/>
+    <xf numFmtId="3" fontId="32" fillId="0" borderId="14"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="12"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="17">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="14"/>
+    <xf numFmtId="173" fontId="37" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="37" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="18" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="28" fillId="0" borderId="13" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="28" fillId="0" borderId="13" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="28" fillId="0" borderId="13" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="28" fillId="0" borderId="13" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="28" fillId="0" borderId="13" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="28" fillId="0" borderId="13" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="28" fillId="0" borderId="13" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="28" fillId="41" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="14" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="43" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="69">
+  <cellStyles count="179">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -820,50 +1188,160 @@
     <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="AF Column - IBM Cognos" xfId="72" xr:uid="{5B288054-91BD-45E7-84D8-7736F17E7C88}"/>
+    <cellStyle name="AF Data - IBM Cognos" xfId="73" xr:uid="{B7AF57DD-224D-4D40-93FB-DDC12520D82C}"/>
+    <cellStyle name="AF Data 0 - IBM Cognos" xfId="74" xr:uid="{4D6FDB12-CCCA-49D8-A7A2-4497B8D9321F}"/>
+    <cellStyle name="AF Data 1 - IBM Cognos" xfId="75" xr:uid="{E2D76BDB-612C-41ED-BF34-F4ED0E05CD98}"/>
+    <cellStyle name="AF Data 2 - IBM Cognos" xfId="76" xr:uid="{0EA79A6B-5B7D-4FBD-B6C7-547A7F06C20B}"/>
+    <cellStyle name="AF Data 3 - IBM Cognos" xfId="77" xr:uid="{8C25C0A0-95E1-4002-A716-D392622DAB25}"/>
+    <cellStyle name="AF Data 4 - IBM Cognos" xfId="78" xr:uid="{6589B5C5-8810-4AF3-9A3A-6DB6B82BF566}"/>
+    <cellStyle name="AF Data 5 - IBM Cognos" xfId="79" xr:uid="{C41ECB30-A495-441F-8D48-AB6822D585DC}"/>
+    <cellStyle name="AF Data Leaf - IBM Cognos" xfId="80" xr:uid="{A43B0AC3-D4AF-4FF8-BC84-EEEDDED7DA0A}"/>
+    <cellStyle name="AF Header - IBM Cognos" xfId="81" xr:uid="{9B8B2715-D990-4FAE-A669-CBC239F91F16}"/>
+    <cellStyle name="AF Header 0 - IBM Cognos" xfId="82" xr:uid="{1C613BD4-279E-4758-BBC8-F86131A57740}"/>
+    <cellStyle name="AF Header 1 - IBM Cognos" xfId="83" xr:uid="{743780C3-542B-4389-9607-2E3E494F33E7}"/>
+    <cellStyle name="AF Header 2 - IBM Cognos" xfId="84" xr:uid="{68585880-DAF9-4038-A0B7-2CD1BCB2D397}"/>
+    <cellStyle name="AF Header 3 - IBM Cognos" xfId="85" xr:uid="{2F537270-27E8-4426-B92B-618B614D633E}"/>
+    <cellStyle name="AF Header 4 - IBM Cognos" xfId="86" xr:uid="{ECBF57D1-0832-43CA-9198-D76D42FF644B}"/>
+    <cellStyle name="AF Header 5 - IBM Cognos" xfId="87" xr:uid="{16BD2634-BCFA-4908-AA71-A220B5BAE125}"/>
+    <cellStyle name="AF Header Leaf - IBM Cognos" xfId="88" xr:uid="{DF25DBAE-050C-40D8-AB0E-D857F9D52AE1}"/>
+    <cellStyle name="AF Row - IBM Cognos" xfId="89" xr:uid="{7973EEC8-1C8F-4856-95C3-6889F4FD6AE7}"/>
+    <cellStyle name="AF Row 0 - IBM Cognos" xfId="90" xr:uid="{2FB42F0D-C95F-4577-B9C8-3E19E8EF7F99}"/>
+    <cellStyle name="AF Row 1 - IBM Cognos" xfId="91" xr:uid="{390A9B30-1BD1-41FE-BD64-9C40E1D05A94}"/>
+    <cellStyle name="AF Row 2 - IBM Cognos" xfId="92" xr:uid="{514BCA0F-5C1E-4E73-A513-2F64594A443D}"/>
+    <cellStyle name="AF Row 3 - IBM Cognos" xfId="93" xr:uid="{AF155E83-B473-4329-A605-7378553ACC83}"/>
+    <cellStyle name="AF Row 4 - IBM Cognos" xfId="94" xr:uid="{6A0CC72E-167D-42F0-9176-E79D9C620AE2}"/>
+    <cellStyle name="AF Row 5 - IBM Cognos" xfId="95" xr:uid="{D1CCA9BB-E634-4319-B331-EDA1E05A5B45}"/>
+    <cellStyle name="AF Row Leaf - IBM Cognos" xfId="96" xr:uid="{5C8FD279-00AE-4512-92C5-4942F7FD8B92}"/>
+    <cellStyle name="AF Subnm - IBM Cognos" xfId="97" xr:uid="{AAA55382-89FF-4747-B1EE-E496F04016AC}"/>
+    <cellStyle name="AF Title - IBM Cognos" xfId="98" xr:uid="{AFAAE91A-F23F-4DD8-AD0D-0020E707D52E}"/>
     <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculated Column - IBM Cognos" xfId="99" xr:uid="{266EB9D8-8D0E-458A-BD96-EE0075F1422D}"/>
+    <cellStyle name="Calculated Column Name - IBM Cognos" xfId="100" xr:uid="{6C3BAFB9-C582-40E6-9AA5-7374A8F406CE}"/>
+    <cellStyle name="Calculated Row - IBM Cognos" xfId="101" xr:uid="{F8454FCB-A702-49A1-A5B0-345DD47AFBD3}"/>
+    <cellStyle name="Calculated Row Name - IBM Cognos" xfId="102" xr:uid="{FC6EB7B9-1126-4DE9-B5F1-6E086D4B23F9}"/>
     <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Column Name - IBM Cognos" xfId="103" xr:uid="{00782AD4-7A15-4B43-9A1E-ECAACD2134B3}"/>
+    <cellStyle name="Column Template - IBM Cognos" xfId="104" xr:uid="{1941A02C-1EB4-4639-ABFF-C1FB54FF9FF6}"/>
     <cellStyle name="Comma [0] 2" xfId="45" xr:uid="{7D630C53-61E4-4A73-9034-71C21859F1C5}"/>
     <cellStyle name="Comma [0] 2 2" xfId="46" xr:uid="{AC9152D1-45A0-421B-9529-52D28B5FB90E}"/>
+    <cellStyle name="Comma [0] 2 3" xfId="139" xr:uid="{1C5A0566-E914-48E4-BC07-C268CCD17075}"/>
     <cellStyle name="Comma 2" xfId="47" xr:uid="{8C067792-97E2-446D-8A6E-99067BA28278}"/>
     <cellStyle name="Comma 2 2" xfId="48" xr:uid="{412988C2-F02D-4B63-B288-8453D514C807}"/>
+    <cellStyle name="Comma 2 3" xfId="128" xr:uid="{96298D70-7A90-4E27-99A3-DCFAE492FDAA}"/>
     <cellStyle name="Comma 2_Technical ID" xfId="49" xr:uid="{77349D71-B47F-4585-B4C7-ECC7D7D859F6}"/>
     <cellStyle name="Comma 3" xfId="50" xr:uid="{2E915666-9583-497E-B538-7B2C8A622D4D}"/>
     <cellStyle name="Comma 3 2" xfId="51" xr:uid="{A5FDA0A6-65E2-4D9A-BBA3-F485FFEF54FC}"/>
+    <cellStyle name="Comma 3 3" xfId="138" xr:uid="{E7B7349E-8927-4B58-9E5D-4EDB5B088118}"/>
     <cellStyle name="Comma 4" xfId="52" xr:uid="{61270FC1-86E8-4C6F-AF87-EE31D79B3859}"/>
     <cellStyle name="Comma 4 2" xfId="53" xr:uid="{5A688B96-F8EF-49D0-A79E-C4AAE7DF994C}"/>
+    <cellStyle name="Comma 4 3" xfId="143" xr:uid="{3938D439-8BEE-4437-A807-8513B22D00A8}"/>
+    <cellStyle name="Comma 5" xfId="164" xr:uid="{48A2B3E6-C82F-43EB-8398-B158616D8195}"/>
+    <cellStyle name="Comma 6" xfId="169" xr:uid="{B275B0B0-88E2-47AC-A90E-2D935D255F69}"/>
     <cellStyle name="Currency [0] 2" xfId="54" xr:uid="{D8477794-CADC-47C0-A975-2038094B0936}"/>
     <cellStyle name="Currency [0] 2 2" xfId="55" xr:uid="{89C37AE0-7BBD-413F-96B5-AD3AE53016E4}"/>
+    <cellStyle name="Currency [0] 2 3" xfId="137" xr:uid="{770EDA87-D02B-4955-99A5-883E630FA44A}"/>
+    <cellStyle name="Currency [0] 3" xfId="168" xr:uid="{F52C5BD8-4C24-417F-A62B-CBE1FE84342C}"/>
     <cellStyle name="Currency 2" xfId="56" xr:uid="{BA62BD7A-4682-4823-A8FE-04149A9DFCE2}"/>
     <cellStyle name="Currency 2 2" xfId="57" xr:uid="{89EDC497-F996-4258-90D7-72EFB05FDEB1}"/>
+    <cellStyle name="Currency 2 3" xfId="136" xr:uid="{093251DA-A7EC-4166-B0FF-B2E5FBDAF939}"/>
     <cellStyle name="Currency 3" xfId="58" xr:uid="{6B24712F-6AE3-4EBB-BC7E-06722FD4D28E}"/>
     <cellStyle name="Currency 3 2" xfId="59" xr:uid="{1F20F655-4157-452B-910E-92FD06CFB4CB}"/>
+    <cellStyle name="Currency 3 3" xfId="142" xr:uid="{6AD3B045-2043-4E4C-9B52-EABD82A97106}"/>
+    <cellStyle name="Currency 4" xfId="167" xr:uid="{7EA2C224-DBE9-429E-A7B6-1AC0D42015AC}"/>
+    <cellStyle name="Differs From Base - IBM Cognos" xfId="105" xr:uid="{9B88EB0E-6ECD-4436-8513-DC20A472E165}"/>
+    <cellStyle name="DQR Column 0 - IBM Cognos" xfId="145" xr:uid="{F746C7B7-CF43-4EAE-99D1-F4EB9C20413B}"/>
+    <cellStyle name="DQR Column 1 - IBM Cognos" xfId="146" xr:uid="{99E743A1-A600-4A46-A52E-68819BB5801F}"/>
+    <cellStyle name="DQR Column 2 - IBM Cognos" xfId="147" xr:uid="{7E935B84-09E4-4892-9480-D203ABA51D36}"/>
+    <cellStyle name="DQR Column 3 - IBM Cognos" xfId="148" xr:uid="{860EFD4E-F38D-46F1-B93D-DDFB69257FF4}"/>
+    <cellStyle name="DQR Column 4 - IBM Cognos" xfId="149" xr:uid="{3851F28A-DDE6-48E3-8F4F-0632DF16BADB}"/>
+    <cellStyle name="DQR Column 5 - IBM Cognos" xfId="150" xr:uid="{8277CDBE-AB98-4761-A443-D3F6ABAF8D37}"/>
+    <cellStyle name="DQR Column Default - IBM Cognos" xfId="151" xr:uid="{B5A046FB-BE19-4EEE-9BC2-4068A3E9932B}"/>
+    <cellStyle name="DQR Column Leaf - IBM Cognos" xfId="152" xr:uid="{A8DECE21-674E-49B2-9F14-6FBFB062E872}"/>
+    <cellStyle name="DQR Data Default - IBM Cognos" xfId="153" xr:uid="{FA86DE84-A2B0-4631-877E-BCFB693AA6E6}"/>
+    <cellStyle name="DQR Data Default - IBM Cognos 2" xfId="173" xr:uid="{E6D9F2A3-1929-4549-B091-FED123D6373E}"/>
+    <cellStyle name="DQR Default - IBM Cognos" xfId="154" xr:uid="{2C7B7C1F-EAD5-4B3B-9C2A-DD5D06461132}"/>
+    <cellStyle name="DQR Gutter Default - IBM Cognos" xfId="170" xr:uid="{F365A995-2B48-4BDF-B8A1-F47C8616F779}"/>
+    <cellStyle name="DQR Gutter Default (OFF) - IBM Cognos" xfId="175" xr:uid="{B0CC87B6-57F9-416D-80C8-AF024E5C6F69}"/>
+    <cellStyle name="DQR Row 0 - IBM Cognos" xfId="155" xr:uid="{486B282B-B847-4498-8599-9BC368506CAB}"/>
+    <cellStyle name="DQR Row 1 - IBM Cognos" xfId="156" xr:uid="{4E458A8B-6E96-4FDA-B4F2-EC9C7F1978F7}"/>
+    <cellStyle name="DQR Row 2 - IBM Cognos" xfId="157" xr:uid="{6D526249-D3F1-433E-BA5B-649FD14732EE}"/>
+    <cellStyle name="DQR Row 3 - IBM Cognos" xfId="158" xr:uid="{C4EE6EFB-603A-4F17-9FAF-7B48B28B6118}"/>
+    <cellStyle name="DQR Row 4 - IBM Cognos" xfId="159" xr:uid="{5B2325D6-C6C2-4E8B-80B6-78B0DF00CB09}"/>
+    <cellStyle name="DQR Row 5 - IBM Cognos" xfId="160" xr:uid="{71B8DE30-7127-42FC-931C-6536DDFFB78F}"/>
+    <cellStyle name="DQR Row Default - IBM Cognos" xfId="161" xr:uid="{A4877E3B-4816-4764-8B37-0DBCE4BA4FAF}"/>
+    <cellStyle name="DQR Row Leaf - IBM Cognos" xfId="162" xr:uid="{B76F18C4-3C75-4594-AE68-8205DB694A9D}"/>
+    <cellStyle name="Edit - IBM Cognos" xfId="106" xr:uid="{37E91FB0-13FF-4837-B956-B7D63334D225}"/>
     <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Formula - IBM Cognos" xfId="107" xr:uid="{7CC8B396-AA60-4CA6-BD5F-55A8039568E3}"/>
     <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Group Name - IBM Cognos" xfId="108" xr:uid="{62F69CA5-628E-466B-A98F-58B78B59F0FD}"/>
     <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hold Values - IBM Cognos" xfId="109" xr:uid="{2E9B3E82-8A5A-4F0C-80DD-4E03E05399A5}"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="List Name - IBM Cognos" xfId="110" xr:uid="{7C48E08D-079C-4D78-BD10-543790F1B545}"/>
+    <cellStyle name="Locked - IBM Cognos" xfId="111" xr:uid="{BB94BD98-1BB8-40EA-B5E4-64DB8C9C3F48}"/>
+    <cellStyle name="Measure - IBM Cognos" xfId="112" xr:uid="{8CA634D0-9F8E-4F5E-AF21-7FB69086D7F8}"/>
+    <cellStyle name="Measure Header - IBM Cognos" xfId="113" xr:uid="{0FA1755A-38B0-4B56-AE07-0BBA0EDABEC1}"/>
+    <cellStyle name="Measure Name - IBM Cognos" xfId="114" xr:uid="{4F211290-1A60-415B-89CB-D3BAB0DBE5D2}"/>
+    <cellStyle name="Measure Summary - IBM Cognos" xfId="115" xr:uid="{79544253-EA4E-45F7-BF54-A5FE5B9139C6}"/>
+    <cellStyle name="Measure Summary TM1 - IBM Cognos" xfId="116" xr:uid="{FC4B44A8-8712-4084-B188-9EB8CB332FD2}"/>
+    <cellStyle name="Measure Template - IBM Cognos" xfId="117" xr:uid="{5968444F-E8E7-4C0F-A4E7-9889D73EC43E}"/>
+    <cellStyle name="More - IBM Cognos" xfId="118" xr:uid="{E245692D-2BDA-4C56-BFC6-BB9F0E93917E}"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
     <cellStyle name="Normal 2" xfId="60" xr:uid="{18AB14A9-467A-4603-BCB6-97E8EB77C35F}"/>
     <cellStyle name="Normal 2 2" xfId="61" xr:uid="{A9A46CDF-DB12-4E5F-AC40-CD86FC03EF2E}"/>
+    <cellStyle name="Normal 2 2 2" xfId="127" xr:uid="{053B206D-8A20-406D-889A-0FB1D571E9B6}"/>
+    <cellStyle name="Normal 2 3" xfId="131" xr:uid="{4F7E3ACD-79F3-44ED-BE8C-2C7FA690F8F8}"/>
+    <cellStyle name="Normal 2 4" xfId="133" xr:uid="{EF5863A8-6062-46BB-BFA4-6E51E9D6A8D0}"/>
+    <cellStyle name="Normal 2 5" xfId="140" xr:uid="{E820259E-580A-4CB5-B87F-666B5A3EDE2F}"/>
+    <cellStyle name="Normal 2 6" xfId="69" xr:uid="{0F784B10-7AD1-4B8E-8848-E3F7B8DB8921}"/>
     <cellStyle name="Normal 2_Dump" xfId="67" xr:uid="{207F9438-393E-41BE-9D3C-6641AE0C45C5}"/>
     <cellStyle name="Normal 227" xfId="62" xr:uid="{C429AFA7-6A01-496D-832D-05BEE8C915D8}"/>
     <cellStyle name="Normal 3" xfId="63" xr:uid="{39D95200-95FA-4F24-9F95-2D618A8BACA8}"/>
+    <cellStyle name="Normal 3 2" xfId="130" xr:uid="{F9297288-4330-4930-9F10-FBF9DC8BFA9A}"/>
+    <cellStyle name="Normal 3 3" xfId="70" xr:uid="{B389B1C1-189E-495C-AC66-07EE59BF3B6F}"/>
     <cellStyle name="Normal 4" xfId="64" xr:uid="{200FBEBD-FD0E-46D0-B03C-2443DF3078DF}"/>
+    <cellStyle name="Normal 4 15" xfId="71" xr:uid="{9B035293-D8EC-4D90-8646-BD35600FCC29}"/>
+    <cellStyle name="Normal 4 2" xfId="144" xr:uid="{E7F865C9-B3A0-40CF-841E-E2F7BC9B160E}"/>
+    <cellStyle name="Normal 4 7 4 5 2 2" xfId="129" xr:uid="{BFEB0FD5-CBBB-4E01-8020-1BD1452E5DC7}"/>
     <cellStyle name="Normal 5" xfId="65" xr:uid="{5F6F2A34-3904-4F86-BC4E-D96107E1FE68}"/>
+    <cellStyle name="Normal 5 2" xfId="163" xr:uid="{FC46A32F-3112-4E35-9025-6A73B2C0A4A0}"/>
+    <cellStyle name="Normal 6" xfId="174" xr:uid="{D8D89457-1348-4A6C-B0C8-7E655A39574A}"/>
+    <cellStyle name="Normal 7" xfId="171" xr:uid="{C028F422-8BEE-421F-9056-6CF5266D101E}"/>
+    <cellStyle name="Normal 72" xfId="178" xr:uid="{B345B7B4-F23E-4612-AC56-151715E28036}"/>
+    <cellStyle name="Normal 8" xfId="172" xr:uid="{9A694FF6-BC33-4C9B-A4DE-42AD854C8733}"/>
+    <cellStyle name="Normal 9" xfId="176" xr:uid="{FFF0BB75-B72A-49E8-B41D-821AFD487B50}"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Pending Change - IBM Cognos" xfId="119" xr:uid="{A7D0703A-7C50-4A23-BD53-49BD496DA876}"/>
     <cellStyle name="Percent 2" xfId="66" xr:uid="{1B6506AF-E707-4DD1-A4C8-1E423C5034B7}"/>
+    <cellStyle name="Percent 2 2" xfId="135" xr:uid="{AEEEB139-3E0B-4FEC-AF1E-9AAC8212242F}"/>
+    <cellStyle name="Row Name - IBM Cognos" xfId="120" xr:uid="{EAE24DC5-4794-427F-B2DE-3DA74AAD3855}"/>
+    <cellStyle name="Row Template - IBM Cognos" xfId="121" xr:uid="{0751B832-CFBF-4C2B-ABD0-40915F901AC1}"/>
+    <cellStyle name="SAPHierarchyCell1" xfId="177" xr:uid="{47EE934C-2CC5-4894-9982-DBC055DD8077}"/>
+    <cellStyle name="SAPHierarchyCell2" xfId="132" xr:uid="{D035D709-4ED8-41B5-A421-D9655CD0F20C}"/>
     <cellStyle name="SAPHierarchyCell3" xfId="68" xr:uid="{46A4C568-C6F8-4BEE-94F0-13D4BF5D6C6D}"/>
+    <cellStyle name="SAPHierarchyCell3 2" xfId="141" xr:uid="{7FE91827-6C88-4270-AC04-84BBC5069557}"/>
     <cellStyle name="SAPHierarchyCell4" xfId="44" xr:uid="{69BC76A9-3113-4D18-A901-065AD296BF03}"/>
     <cellStyle name="SAPMemberCell" xfId="42" xr:uid="{D343716C-7F9F-42C4-AD39-5487396524E0}"/>
     <cellStyle name="SAPMemberTotalCell" xfId="43" xr:uid="{D8829FE3-8E04-4702-A669-8D7221854A11}"/>
+    <cellStyle name="Standard 2" xfId="134" xr:uid="{1540CAC1-F72A-497E-8850-2D913F777137}"/>
+    <cellStyle name="Standard 2 2" xfId="166" xr:uid="{22C77DA5-B9B7-446D-936C-EDE598EA61F3}"/>
+    <cellStyle name="Standard_Test_FR21_YI05" xfId="165" xr:uid="{965853DA-EE27-4924-9061-1E2619D6DD72}"/>
+    <cellStyle name="Summary Column Name - IBM Cognos" xfId="122" xr:uid="{519A3858-31BC-4B92-A047-15979346B365}"/>
+    <cellStyle name="Summary Column Name TM1 - IBM Cognos" xfId="123" xr:uid="{E0170AF9-7344-428F-8797-DA687C4E05F1}"/>
+    <cellStyle name="Summary Row Name - IBM Cognos" xfId="124" xr:uid="{F216ED16-3D19-4087-9F48-BE6A923DBDAB}"/>
+    <cellStyle name="Summary Row Name TM1 - IBM Cognos" xfId="125" xr:uid="{A677EE73-E61C-484A-BC4D-4EF25A19B191}"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Unsaved Change - IBM Cognos" xfId="126" xr:uid="{11FCD23F-52C8-4677-ABCE-6F010B721CAD}"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="2">
@@ -888,7 +1366,9 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{5EF786B8-8D85-4DAC-9788-B230CB0445FC}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1198,7 +1678,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BF5FEE-4834-415E-A288-F1664A2A6DF0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1207,15 +1687,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9544D389-BCBF-4017-8282-1DF88DB28091}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="51.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1226,191 +1706,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C2" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Inputs/PyDump.xlsx
+++ b/Inputs/PyDump.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M289204\Documents\GCOH\GCOH-Tickets-for-Processing\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73804670-5CA4-429A-9FE9-8358C73DC82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B605C418-C791-4C85-9521-9333286C9E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6360" yWindow="2430" windowWidth="21600" windowHeight="12255" firstSheet="1" activeTab="1" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{6A12B107-397F-4BA6-8F78-4BB99A484E33}"/>
   </bookViews>
   <sheets>
     <sheet name="Cognos_Office_Connection_Cache" sheetId="2" state="veryHidden" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="132">
   <si>
     <t>Object</t>
   </si>
@@ -60,6 +60,384 @@
   </si>
   <si>
     <t>FR8941660</t>
+  </si>
+  <si>
+    <t>PLEAN_X310201CZ5000000 Fertility Commercial CZ50</t>
+  </si>
+  <si>
+    <t>H000002141</t>
+  </si>
+  <si>
+    <t>PLEAN_X310201CZ5010000 Fertility Commercial CZ50 Promo Material</t>
+  </si>
+  <si>
+    <t>PLEAN_X310201CZ5011000 Fertility Commercial CZ50 Advertising</t>
+  </si>
+  <si>
+    <t>PLEAN_X310201CZ5013000 Fertility Commercial CZ50 Congress &amp; Eve</t>
+  </si>
+  <si>
+    <t>PLEAN_X310201CZ5013201 Fertility Commercial CZ50 Congress &amp; Eve</t>
+  </si>
+  <si>
+    <t>PLEAN_X310201CZ5015000 Fertility Commercial CZ50 Other Promo an</t>
+  </si>
+  <si>
+    <t>PLEAN_X310201CZ5015205 Fertility Commercial CZ50 Other Promo an</t>
+  </si>
+  <si>
+    <t>PLEAN_X310201CZ5030000 Fertility Commercial CZ50 Other M&amp;S Regi</t>
+  </si>
+  <si>
+    <t>PLEAN_X310201CZ5030207 Fertility Commercial CZ50 Other M&amp;S Regi</t>
+  </si>
+  <si>
+    <t>PLEAN_X310301CZ5000000 Gluco Commercial CZ50</t>
+  </si>
+  <si>
+    <t>PLEAN_X310301CZ5010000 Gluco Commercial CZ50 Promo Material</t>
+  </si>
+  <si>
+    <t>PLEAN_X310301CZ5011000 Gluco Commercial CZ50 Advertising</t>
+  </si>
+  <si>
+    <t>PLEAN_X310301CZ5013000 Gluco Commercial CZ50 Congress &amp; Events</t>
+  </si>
+  <si>
+    <t>PLEAN_X310301CZ5013203 Gluco Commercial CZ50 Congress &amp; Events</t>
+  </si>
+  <si>
+    <t>PLEAN_X310301CZ5015000 Gluco Commercial CZ50 Other Promo and Ad</t>
+  </si>
+  <si>
+    <t>PLEAN_X310301CZ5030000 Gluco Commercial CZ50 Other M&amp;S Registra</t>
+  </si>
+  <si>
+    <t>PLEAN_X310301CZ5030207 Gluco Commercial CZ50 Other M&amp;S Registra</t>
+  </si>
+  <si>
+    <t>PLEAN_X310321CZ5013203 Cardio Commercial CZ50 Congress &amp; Events</t>
+  </si>
+  <si>
+    <t>PLEAN_X310321CZ5013204 Cardio Commercial CZ50 Congress &amp; Events</t>
+  </si>
+  <si>
+    <t>PLEAN_X310321CZ5030207 Cardio Commercial CZ50 Other M&amp;S Registr</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5000000 GM KGAA Commercial CZ50</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5010000 GM KGAA Commercial CZ50 Promo Material</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5010201 GM KGAA Commercial CZ50 Promo Material G</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5011000 GM KGAA Commercial CZ50 Advertising</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5011201 GM KGAA Commercial CZ50 Advertising Gene</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5013000 GM KGAA Commercial CZ50 Congress &amp; Event</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5013201 GM KGAA Commercial CZ50 Congress &amp; Event</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5013202 GM KGAA Commercial CZ50 Congress &amp; Event</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5013203 GM KGAA Commercial CZ50 Congress &amp; Event</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5013204 GM KGAA Commercial CZ50 Congress &amp; Event</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5013205 GM KGAA Commercial CZ50 Congress &amp; Event</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5015000 GM KGAA Commercial CZ50 Other Promo and</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5015201 GM KGAA Commercial CZ50 Other Promo and</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5015205 GM KGAA Commercial CZ50 Other Promo and</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5030000 GM KGAA Commercial CZ50 Other M&amp;S Regist</t>
+  </si>
+  <si>
+    <t>PLEAN_X310351CZ5030207 GM KGAA Commercial CZ50 Other M&amp;S Regist</t>
+  </si>
+  <si>
+    <t>PLEAN_X310401CZ5000000 Saizen Commercial CZ50</t>
+  </si>
+  <si>
+    <t>PLEAN_X310401CZ5010000 Saizen Commercial CZ50 Promo Material</t>
+  </si>
+  <si>
+    <t>PLEAN_X310401CZ5011000 Saizen Commercial CZ50 Advertising</t>
+  </si>
+  <si>
+    <t>PLEAN_X310401CZ5013000 Saizen Commercial CZ50 Congress &amp; Events</t>
+  </si>
+  <si>
+    <t>PLEAN_X310401CZ5013201 Saizen Commercial CZ50 Congress &amp; Events</t>
+  </si>
+  <si>
+    <t>PLEAN_X310401CZ5013205 Saizen Commercial CZ50 Congress &amp; Events</t>
+  </si>
+  <si>
+    <t>PLEAN_X310401CZ5015000 Saizen Commercial CZ50 Other Promo and A</t>
+  </si>
+  <si>
+    <t>PLEAN_X310401CZ5030000 Saizen Commercial CZ50 Other M&amp;S Registr</t>
+  </si>
+  <si>
+    <t>PLEAN_X310401CZ5030207 Saizen Commercial CZ50 Other M&amp;S Registr</t>
+  </si>
+  <si>
+    <t>PLEAN_X310402CZ5020201 Saizen Medical Non R&amp;D CZ50 Medical Educ</t>
+  </si>
+  <si>
+    <t>PLEAN_X310402CZ5020203 Saizen Medical Non R&amp;D CZ50 Medical Educ</t>
+  </si>
+  <si>
+    <t>PLEAN_X310402CZ5020205 Saizen Medical Non R&amp;D CZ50 Medical Educ</t>
+  </si>
+  <si>
+    <t>PLEAN_X310402CZ5020206 Saizen Medical Non R&amp;D CZ50 Medical Educ</t>
+  </si>
+  <si>
+    <t>PLEAN_X310402CZ5021201 Saizen Medical Non R&amp;D CZ50 Medical Dona</t>
+  </si>
+  <si>
+    <t>PLEAN_X310402CZ5022201 Saizen Medical Non R&amp;D CZ50 Medical Cons</t>
+  </si>
+  <si>
+    <t>PLEAN_X310502CZ5020201 Rebif Medical Non R&amp;D CZ50 Medical Educa</t>
+  </si>
+  <si>
+    <t>PLEAN_X310502CZ5020202 Rebif Medical Non R&amp;D CZ50 Medical Educa</t>
+  </si>
+  <si>
+    <t>PLEAN_X310502CZ5020203 Rebif Medical Non R&amp;D CZ50 Medical Educa</t>
+  </si>
+  <si>
+    <t>PLEAN_X310502CZ5020205 Rebif Medical Non R&amp;D CZ50 Medical Educa</t>
+  </si>
+  <si>
+    <t>PLEAN_X310502CZ5020206 Rebif Medical Non R&amp;D CZ50 Medical Educa</t>
+  </si>
+  <si>
+    <t>PLEAN_X310502CZ5021201 Rebif Medical Non R&amp;D CZ50 Medical Donat</t>
+  </si>
+  <si>
+    <t>PLEAN_X310502CZ5022201 Rebif Medical Non R&amp;D CZ50 Medical Consu</t>
+  </si>
+  <si>
+    <t>PLEAN_X310502CZ5023201 Rebif Medical Non R&amp;D CZ50 Other Medical</t>
+  </si>
+  <si>
+    <t>PLEAN_X310502CZ5023205 Rebif Medical Non R&amp;D CZ50 Other Medical</t>
+  </si>
+  <si>
+    <t>PLEAN_X310511CZ5000000 Mavenclad Commercial CZ50</t>
+  </si>
+  <si>
+    <t>PLEAN_X310511CZ5010000 Mavenclad Commercial CZ50 Promo Material</t>
+  </si>
+  <si>
+    <t>PLEAN_X310511CZ5011000 Mavenclad Commercial CZ50 Advertising</t>
+  </si>
+  <si>
+    <t>PLEAN_X310511CZ5013000 Mavenclad Commercial CZ50 Congress &amp; Eve</t>
+  </si>
+  <si>
+    <t>PLEAN_X310511CZ5015000 Mavenclad Commercial CZ50 Other Promo an</t>
+  </si>
+  <si>
+    <t>PLEAN_X310511CZ5030000 Mavenclad Commercial CZ50 Other M&amp;S Regi</t>
+  </si>
+  <si>
+    <t>PLEAN_X310512CZ5020201 Mavenclad Medical Non R&amp;D CZ50 Medical E</t>
+  </si>
+  <si>
+    <t>PLEAN_X310512CZ5020206 Mavenclad Medical Non R&amp;D CZ50 Medical E</t>
+  </si>
+  <si>
+    <t>PLEAN_X310512CZ5023205 Mavenclad Medical Non R&amp;D CZ50 Other Med</t>
+  </si>
+  <si>
+    <t>PLEAN_X310513CZ5000000 Mavenclad Local R&amp;D CZ50</t>
+  </si>
+  <si>
+    <t>PLEAN_X310513CZ5043201 Mavenclad Local R&amp;D CZ50 Local R&amp;D Gener</t>
+  </si>
+  <si>
+    <t>PLEAN_X310513CZ5043208 Mavenclad Local R&amp;D CZ50 Local R&amp;D Ready</t>
+  </si>
+  <si>
+    <t>PLEAN_X310513CZ5043209 Mavenclad Local R&amp;D CZ50 Local R&amp;D Profi</t>
+  </si>
+  <si>
+    <t>PLEAN_X370221CZ5015201 Ogsiveo Commercial CZ50 Other Promotion</t>
+  </si>
+  <si>
+    <t>PLEAN_X370222CZ5021201 Ogsiveo Medical CZ50 Donations General C</t>
+  </si>
+  <si>
+    <t>PLEAN_X370231CZ5010201 Gomekli/Ezmekly Commercial CZ50 Promotio</t>
+  </si>
+  <si>
+    <t>PLEAN_X370231CZ5015201 Gomekli/Ezmekly Commercial CZ50 Other Pr</t>
+  </si>
+  <si>
+    <t>PLEAN_X370232CZ5021201 Gomekli/Ezmekly Medical CZ50 Medical Don</t>
+  </si>
+  <si>
+    <t>CFLTFLE_23762376G1100 FINANCE</t>
+  </si>
+  <si>
+    <t>P000000751 GK2 CP - Controlling Electronics (L2)</t>
+  </si>
+  <si>
+    <t>CFLTFLE_23762376G1400 HR</t>
+  </si>
+  <si>
+    <t>P000000757 EL-BP-H HR Business Partner</t>
+  </si>
+  <si>
+    <t>IQUATRO_006000000620 XXXUS01IC1188ROY3212700000</t>
+  </si>
+  <si>
+    <t>P000001493 EL Technical Objects</t>
+  </si>
+  <si>
+    <t>IQUATRO_001030000160 Royalty_R&amp;D</t>
+  </si>
+  <si>
+    <t>D00147000000000 GVO-OLED-mobile-VM13 KR</t>
+  </si>
+  <si>
+    <t>P000001230 GVO</t>
+  </si>
+  <si>
+    <t>D00149800000000 OLED HTM_Supply Materials</t>
+  </si>
+  <si>
+    <t>P000001235 HTM</t>
+  </si>
+  <si>
+    <t>D00149900000000 OLED TMM_Probenversand</t>
+  </si>
+  <si>
+    <t>P000001236 TMM</t>
+  </si>
+  <si>
+    <t>D00150000000000 OLED TMM_Supply Materials</t>
+  </si>
+  <si>
+    <t>D00150100000000 BOE-mobile-Q13 KR</t>
+  </si>
+  <si>
+    <t>P000001228 BOE</t>
+  </si>
+  <si>
+    <t>D00150200000000 BOE-mobile-Q13</t>
+  </si>
+  <si>
+    <t>D00151200000000 LGD-OLED-mobile-RDL</t>
+  </si>
+  <si>
+    <t>P000001232 LGD</t>
+  </si>
+  <si>
+    <t>D00151700000000 CSOT-OLED-Mobile-C13</t>
+  </si>
+  <si>
+    <t>P000001229 CSOT</t>
+  </si>
+  <si>
+    <t>D00000600000000 LC Smart Windows</t>
+  </si>
+  <si>
+    <t>P000001267 Dynamic Glazing</t>
+  </si>
+  <si>
+    <t>D00023600000000 Other Display Technologies</t>
+  </si>
+  <si>
+    <t>D00120200000000 LCW R&amp;D IC Charge</t>
+  </si>
+  <si>
+    <t>D00121900000000 LCW R&amp;D CrossCharge</t>
+  </si>
+  <si>
+    <t>CTEMPEU_1000GB40000780 ARVR PVH BD</t>
+  </si>
+  <si>
+    <t>P000001134 EL-OP-B Business Strategy &amp; Service Head</t>
+  </si>
+  <si>
+    <t>PLEAN_X370221CZ5011201 Ogsiveo Commercial CZ50 Advertising Gene</t>
+  </si>
+  <si>
+    <t>PLEAN_X370221CZ5013201 Ogsiveo Commercial CZ50 Congresses &amp; Eve</t>
+  </si>
+  <si>
+    <t>PLEAN_X370231CZ5011201 Gomekli/Ezmekly Commercial CZ50 Advertis</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203801101 PM/OD- Import/Export</t>
+  </si>
+  <si>
+    <t>L000009288</t>
+  </si>
+  <si>
+    <t>CEMERAL_70006203801112 PM/OD- Import/Export</t>
+  </si>
+  <si>
+    <t>CEMERAL_64010010981107 Engineering/EHS Dept- ADC Site</t>
+  </si>
+  <si>
+    <t>L000009293</t>
+  </si>
+  <si>
+    <t>CNOW_ROW$$$$0000005222 JP DISTIBUTION Lab Water Warehouse</t>
+  </si>
+  <si>
+    <t>L000009294</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.2621 2621 MM Demand planning</t>
+  </si>
+  <si>
+    <t>L000013797</t>
+  </si>
+  <si>
+    <t>CORAERP_MMOR1945.2623 2623 MM Supply network planning</t>
+  </si>
+  <si>
+    <t>CNOW_7210$$$0000023301 LS-ODR - Research &amp; Applied</t>
+  </si>
+  <si>
+    <t>CPHOENX_01010000607400 LS-ODR SC Research and Applied</t>
+  </si>
+  <si>
+    <t>FR8945639</t>
+  </si>
+  <si>
+    <t>FR8953280</t>
+  </si>
+  <si>
+    <t>FR8945072</t>
+  </si>
+  <si>
+    <t>FR8946325</t>
   </si>
 </sst>
 </file>
@@ -1687,7 +2065,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9544D389-BCBF-4017-8282-1DF88DB28091}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="51.85546875" bestFit="1" customWidth="1"/>
@@ -1715,6 +2093,1172 @@
       </c>
       <c r="C2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" t="s">
+        <v>86</v>
+      </c>
+      <c r="C81" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>87</v>
+      </c>
+      <c r="B82" t="s">
+        <v>88</v>
+      </c>
+      <c r="C82" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" t="s">
+        <v>90</v>
+      </c>
+      <c r="C83" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" t="s">
+        <v>90</v>
+      </c>
+      <c r="C84" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" t="s">
+        <v>93</v>
+      </c>
+      <c r="C85" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" t="s">
+        <v>95</v>
+      </c>
+      <c r="C86" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>96</v>
+      </c>
+      <c r="B87" t="s">
+        <v>97</v>
+      </c>
+      <c r="C87" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>98</v>
+      </c>
+      <c r="B88" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>99</v>
+      </c>
+      <c r="B89" t="s">
+        <v>100</v>
+      </c>
+      <c r="C89" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>101</v>
+      </c>
+      <c r="B90" t="s">
+        <v>100</v>
+      </c>
+      <c r="C90" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>102</v>
+      </c>
+      <c r="B91" t="s">
+        <v>103</v>
+      </c>
+      <c r="C91" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>104</v>
+      </c>
+      <c r="B92" t="s">
+        <v>105</v>
+      </c>
+      <c r="C92" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>106</v>
+      </c>
+      <c r="B93" t="s">
+        <v>107</v>
+      </c>
+      <c r="C93" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>108</v>
+      </c>
+      <c r="B94" t="s">
+        <v>107</v>
+      </c>
+      <c r="C94" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>109</v>
+      </c>
+      <c r="B95" t="s">
+        <v>107</v>
+      </c>
+      <c r="C95" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>110</v>
+      </c>
+      <c r="B96" t="s">
+        <v>107</v>
+      </c>
+      <c r="C96" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>111</v>
+      </c>
+      <c r="B97" t="s">
+        <v>112</v>
+      </c>
+      <c r="C97" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>113</v>
+      </c>
+      <c r="B98" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>114</v>
+      </c>
+      <c r="B99" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>115</v>
+      </c>
+      <c r="B100" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>116</v>
+      </c>
+      <c r="B101" t="s">
+        <v>117</v>
+      </c>
+      <c r="C101" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>118</v>
+      </c>
+      <c r="B102" t="s">
+        <v>117</v>
+      </c>
+      <c r="C102" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>119</v>
+      </c>
+      <c r="B103" t="s">
+        <v>120</v>
+      </c>
+      <c r="C103" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
+        <v>121</v>
+      </c>
+      <c r="B104" t="s">
+        <v>122</v>
+      </c>
+      <c r="C104" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
+        <v>123</v>
+      </c>
+      <c r="B105" t="s">
+        <v>124</v>
+      </c>
+      <c r="C105" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>125</v>
+      </c>
+      <c r="B106" t="s">
+        <v>124</v>
+      </c>
+      <c r="C106" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
+        <v>126</v>
+      </c>
+      <c r="B107" t="s">
+        <v>124</v>
+      </c>
+      <c r="C107" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>127</v>
+      </c>
+      <c r="B108" t="s">
+        <v>124</v>
+      </c>
+      <c r="C108" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
